--- a/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_Checkpoint_duration_mean_median_stats_df.xlsx
+++ b/TOR330 Data/5. Clean Data for Data Visualisation/TOR330_Checkpoint_duration_mean_median_stats_df.xlsx
@@ -579,16 +579,16 @@
         <v>22</v>
       </c>
       <c r="C2">
-        <v>494</v>
+        <v>3806</v>
       </c>
       <c r="D2">
-        <v>12733</v>
+        <v>12404</v>
       </c>
       <c r="E2">
-        <v>12320</v>
+        <v>12406</v>
       </c>
       <c r="F2">
-        <v>2188</v>
+        <v>1465</v>
       </c>
       <c r="G2">
         <v>8913</v>
@@ -597,10 +597,10 @@
         <v>21942</v>
       </c>
       <c r="I2">
-        <v>12733</v>
+        <v>12404</v>
       </c>
       <c r="J2">
-        <v>12320</v>
+        <v>12406</v>
       </c>
       <c r="K2" t="s">
         <v>41</v>
@@ -614,16 +614,16 @@
         <v>22</v>
       </c>
       <c r="C3">
-        <v>78</v>
+        <v>678</v>
       </c>
       <c r="D3">
-        <v>10333</v>
+        <v>10347</v>
       </c>
       <c r="E3">
-        <v>10183</v>
+        <v>10139</v>
       </c>
       <c r="F3">
-        <v>1177</v>
+        <v>797</v>
       </c>
       <c r="G3">
         <v>8291</v>
@@ -632,10 +632,10 @@
         <v>17390</v>
       </c>
       <c r="I3">
-        <v>10333</v>
+        <v>10347</v>
       </c>
       <c r="J3">
-        <v>10183</v>
+        <v>10139</v>
       </c>
       <c r="K3" t="s">
         <v>41</v>
@@ -649,16 +649,16 @@
         <v>22</v>
       </c>
       <c r="C4">
-        <v>175</v>
+        <v>1039</v>
       </c>
       <c r="D4">
-        <v>11283</v>
+        <v>10909</v>
       </c>
       <c r="E4">
-        <v>10929</v>
+        <v>10701</v>
       </c>
       <c r="F4">
-        <v>1921</v>
+        <v>1291</v>
       </c>
       <c r="G4">
         <v>8877</v>
@@ -667,10 +667,10 @@
         <v>19770</v>
       </c>
       <c r="I4">
-        <v>11283</v>
+        <v>10909</v>
       </c>
       <c r="J4">
-        <v>10929</v>
+        <v>10701</v>
       </c>
       <c r="K4" t="s">
         <v>41</v>
@@ -684,16 +684,16 @@
         <v>22</v>
       </c>
       <c r="C5">
-        <v>212</v>
+        <v>1676</v>
       </c>
       <c r="D5">
-        <v>12079</v>
+        <v>11899</v>
       </c>
       <c r="E5">
-        <v>11706</v>
+        <v>11575</v>
       </c>
       <c r="F5">
-        <v>2013</v>
+        <v>1648</v>
       </c>
       <c r="G5">
         <v>9291</v>
@@ -702,10 +702,10 @@
         <v>21590</v>
       </c>
       <c r="I5">
-        <v>12079</v>
+        <v>11899</v>
       </c>
       <c r="J5">
-        <v>11706</v>
+        <v>11575</v>
       </c>
       <c r="K5" t="s">
         <v>41</v>
@@ -719,16 +719,16 @@
         <v>22</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D6">
-        <v>18968</v>
+        <v>16057</v>
       </c>
       <c r="E6">
-        <v>20684</v>
+        <v>16072</v>
       </c>
       <c r="F6">
-        <v>3420</v>
+        <v>2606</v>
       </c>
       <c r="G6">
         <v>13981</v>
@@ -737,10 +737,10 @@
         <v>23751</v>
       </c>
       <c r="I6">
-        <v>18968</v>
+        <v>16057</v>
       </c>
       <c r="J6">
-        <v>20684</v>
+        <v>16072</v>
       </c>
       <c r="K6" t="s">
         <v>41</v>
@@ -754,16 +754,16 @@
         <v>22</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D7">
-        <v>8326</v>
+        <v>8611</v>
       </c>
       <c r="E7">
-        <v>8354</v>
+        <v>8419</v>
       </c>
       <c r="F7">
-        <v>359</v>
+        <v>253</v>
       </c>
       <c r="G7">
         <v>7992</v>
@@ -772,10 +772,10 @@
         <v>8863</v>
       </c>
       <c r="I7">
-        <v>8326</v>
+        <v>8611</v>
       </c>
       <c r="J7">
-        <v>8354</v>
+        <v>8419</v>
       </c>
       <c r="K7" t="s">
         <v>41</v>
@@ -789,16 +789,16 @@
         <v>22</v>
       </c>
       <c r="C8">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D8">
-        <v>9757</v>
+        <v>9629</v>
       </c>
       <c r="E8">
-        <v>9501</v>
+        <v>9511</v>
       </c>
       <c r="F8">
-        <v>1286</v>
+        <v>937</v>
       </c>
       <c r="G8">
         <v>8384</v>
@@ -807,10 +807,10 @@
         <v>16424</v>
       </c>
       <c r="I8">
-        <v>9757</v>
+        <v>9629</v>
       </c>
       <c r="J8">
-        <v>9501</v>
+        <v>9511</v>
       </c>
       <c r="K8" t="s">
         <v>41</v>
@@ -824,16 +824,16 @@
         <v>22</v>
       </c>
       <c r="C9">
-        <v>1292</v>
+        <v>12476</v>
       </c>
       <c r="D9">
-        <v>14981</v>
+        <v>14457</v>
       </c>
       <c r="E9">
-        <v>14596</v>
+        <v>14584</v>
       </c>
       <c r="F9">
-        <v>3544</v>
+        <v>2546</v>
       </c>
       <c r="G9">
         <v>5660</v>
@@ -842,10 +842,10 @@
         <v>30293</v>
       </c>
       <c r="I9">
-        <v>14981</v>
+        <v>14457</v>
       </c>
       <c r="J9">
-        <v>14596</v>
+        <v>14584</v>
       </c>
       <c r="K9" t="s">
         <v>41</v>
@@ -859,16 +859,16 @@
         <v>22</v>
       </c>
       <c r="C10">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D10">
-        <v>8898</v>
+        <v>9096</v>
       </c>
       <c r="E10">
-        <v>8640</v>
+        <v>8553</v>
       </c>
       <c r="F10">
-        <v>642</v>
+        <v>838</v>
       </c>
       <c r="G10">
         <v>8265</v>
@@ -877,10 +877,10 @@
         <v>10491</v>
       </c>
       <c r="I10">
-        <v>8898</v>
+        <v>9096</v>
       </c>
       <c r="J10">
-        <v>8640</v>
+        <v>8553</v>
       </c>
       <c r="K10" t="s">
         <v>41</v>
@@ -894,16 +894,16 @@
         <v>22</v>
       </c>
       <c r="C11">
-        <v>601</v>
+        <v>6001</v>
       </c>
       <c r="D11">
-        <v>14949</v>
+        <v>14227</v>
       </c>
       <c r="E11">
-        <v>14245</v>
+        <v>14202</v>
       </c>
       <c r="F11">
-        <v>2835</v>
+        <v>1625</v>
       </c>
       <c r="G11">
         <v>7691</v>
@@ -912,10 +912,10 @@
         <v>24445</v>
       </c>
       <c r="I11">
-        <v>14949</v>
+        <v>14227</v>
       </c>
       <c r="J11">
-        <v>14245</v>
+        <v>14202</v>
       </c>
       <c r="K11" t="s">
         <v>41</v>
@@ -929,16 +929,16 @@
         <v>22</v>
       </c>
       <c r="C12">
-        <v>337</v>
+        <v>3049</v>
       </c>
       <c r="D12">
-        <v>13564</v>
+        <v>13487</v>
       </c>
       <c r="E12">
-        <v>13136</v>
+        <v>13270</v>
       </c>
       <c r="F12">
-        <v>2147</v>
+        <v>1496</v>
       </c>
       <c r="G12">
         <v>9672</v>
@@ -947,10 +947,10 @@
         <v>21949</v>
       </c>
       <c r="I12">
-        <v>13564</v>
+        <v>13487</v>
       </c>
       <c r="J12">
-        <v>13136</v>
+        <v>13270</v>
       </c>
       <c r="K12" t="s">
         <v>41</v>
@@ -964,16 +964,16 @@
         <v>23</v>
       </c>
       <c r="C13">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D13">
-        <v>20752</v>
+        <v>21098</v>
       </c>
       <c r="E13">
-        <v>20429</v>
+        <v>21255</v>
       </c>
       <c r="F13">
-        <v>1436</v>
+        <v>1713</v>
       </c>
       <c r="G13">
         <v>17211</v>
@@ -982,10 +982,10 @@
         <v>23421</v>
       </c>
       <c r="I13">
-        <v>30509</v>
+        <v>30727</v>
       </c>
       <c r="J13">
-        <v>29930</v>
+        <v>30766</v>
       </c>
       <c r="K13" t="s">
         <v>41</v>
@@ -999,16 +999,16 @@
         <v>23</v>
       </c>
       <c r="C14">
-        <v>601</v>
+        <v>6001</v>
       </c>
       <c r="D14">
-        <v>33474</v>
+        <v>33871</v>
       </c>
       <c r="E14">
-        <v>33316</v>
+        <v>33848</v>
       </c>
       <c r="F14">
-        <v>3350</v>
+        <v>3094</v>
       </c>
       <c r="G14">
         <v>25535</v>
@@ -1017,10 +1017,10 @@
         <v>50092</v>
       </c>
       <c r="I14">
-        <v>48423</v>
+        <v>48098</v>
       </c>
       <c r="J14">
-        <v>47561</v>
+        <v>48050</v>
       </c>
       <c r="K14" t="s">
         <v>41</v>
@@ -1034,16 +1034,16 @@
         <v>23</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D15">
-        <v>17221</v>
+        <v>17200</v>
       </c>
       <c r="E15">
         <v>17283</v>
       </c>
       <c r="F15">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G15">
         <v>17112</v>
@@ -1052,10 +1052,10 @@
         <v>17296</v>
       </c>
       <c r="I15">
-        <v>25547</v>
+        <v>25811</v>
       </c>
       <c r="J15">
-        <v>25637</v>
+        <v>25702</v>
       </c>
       <c r="K15" t="s">
         <v>41</v>
@@ -1069,16 +1069,16 @@
         <v>23</v>
       </c>
       <c r="C16">
-        <v>492</v>
+        <v>3804</v>
       </c>
       <c r="D16">
-        <v>28414</v>
+        <v>28790</v>
       </c>
       <c r="E16">
-        <v>28310</v>
+        <v>28792</v>
       </c>
       <c r="F16">
-        <v>2771</v>
+        <v>2727</v>
       </c>
       <c r="G16">
         <v>20794</v>
@@ -1087,10 +1087,10 @@
         <v>40888</v>
       </c>
       <c r="I16">
-        <v>41147</v>
+        <v>41194</v>
       </c>
       <c r="J16">
-        <v>40630</v>
+        <v>41198</v>
       </c>
       <c r="K16" t="s">
         <v>41</v>
@@ -1104,16 +1104,16 @@
         <v>23</v>
       </c>
       <c r="C17">
-        <v>1176</v>
+        <v>11472</v>
       </c>
       <c r="D17">
-        <v>34050</v>
+        <v>34788</v>
       </c>
       <c r="E17">
-        <v>34612</v>
+        <v>35345</v>
       </c>
       <c r="F17">
-        <v>6487</v>
+        <v>6332</v>
       </c>
       <c r="G17">
         <v>5324</v>
@@ -1122,10 +1122,10 @@
         <v>52153</v>
       </c>
       <c r="I17">
-        <v>49031</v>
+        <v>49245</v>
       </c>
       <c r="J17">
-        <v>49208</v>
+        <v>49929</v>
       </c>
       <c r="K17" t="s">
         <v>41</v>
@@ -1139,16 +1139,16 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>175</v>
+        <v>1039</v>
       </c>
       <c r="D18">
-        <v>24342</v>
+        <v>24610</v>
       </c>
       <c r="E18">
-        <v>24166</v>
+        <v>24085</v>
       </c>
       <c r="F18">
-        <v>2204</v>
+        <v>2326</v>
       </c>
       <c r="G18">
         <v>19132</v>
@@ -1157,10 +1157,10 @@
         <v>30938</v>
       </c>
       <c r="I18">
-        <v>35625</v>
+        <v>35519</v>
       </c>
       <c r="J18">
-        <v>35095</v>
+        <v>34786</v>
       </c>
       <c r="K18" t="s">
         <v>41</v>
@@ -1174,16 +1174,16 @@
         <v>23</v>
       </c>
       <c r="C19">
-        <v>337</v>
+        <v>3049</v>
       </c>
       <c r="D19">
-        <v>30458</v>
+        <v>31265</v>
       </c>
       <c r="E19">
-        <v>30402</v>
+        <v>31117</v>
       </c>
       <c r="F19">
-        <v>2930</v>
+        <v>3195</v>
       </c>
       <c r="G19">
         <v>22802</v>
@@ -1192,10 +1192,10 @@
         <v>44079</v>
       </c>
       <c r="I19">
-        <v>44022</v>
+        <v>44752</v>
       </c>
       <c r="J19">
-        <v>43538</v>
+        <v>44387</v>
       </c>
       <c r="K19" t="s">
         <v>41</v>
@@ -1209,16 +1209,16 @@
         <v>23</v>
       </c>
       <c r="C20">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D20">
-        <v>18554</v>
+        <v>18850</v>
       </c>
       <c r="E20">
-        <v>18204</v>
+        <v>18135</v>
       </c>
       <c r="F20">
-        <v>1146</v>
+        <v>1274</v>
       </c>
       <c r="G20">
         <v>16772</v>
@@ -1227,10 +1227,10 @@
         <v>21548</v>
       </c>
       <c r="I20">
-        <v>27452</v>
+        <v>27946</v>
       </c>
       <c r="J20">
-        <v>26844</v>
+        <v>26688</v>
       </c>
       <c r="K20" t="s">
         <v>41</v>
@@ -1244,16 +1244,16 @@
         <v>23</v>
       </c>
       <c r="C21">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D21">
-        <v>35884</v>
+        <v>35419</v>
       </c>
       <c r="E21">
         <v>37347</v>
       </c>
       <c r="F21">
-        <v>2759</v>
+        <v>3680</v>
       </c>
       <c r="G21">
         <v>31329</v>
@@ -1262,10 +1262,10 @@
         <v>39322</v>
       </c>
       <c r="I21">
-        <v>54852</v>
+        <v>51476</v>
       </c>
       <c r="J21">
-        <v>58031</v>
+        <v>53419</v>
       </c>
       <c r="K21" t="s">
         <v>41</v>
@@ -1279,16 +1279,16 @@
         <v>23</v>
       </c>
       <c r="C22">
-        <v>211</v>
+        <v>1675</v>
       </c>
       <c r="D22">
-        <v>26504</v>
+        <v>26998</v>
       </c>
       <c r="E22">
-        <v>26354</v>
+        <v>27027</v>
       </c>
       <c r="F22">
-        <v>2243</v>
+        <v>2078</v>
       </c>
       <c r="G22">
         <v>21629</v>
@@ -1297,10 +1297,10 @@
         <v>33377</v>
       </c>
       <c r="I22">
-        <v>38583</v>
+        <v>38897</v>
       </c>
       <c r="J22">
-        <v>38060</v>
+        <v>38602</v>
       </c>
       <c r="K22" t="s">
         <v>41</v>
@@ -1314,16 +1314,16 @@
         <v>23</v>
       </c>
       <c r="C23">
-        <v>78</v>
+        <v>678</v>
       </c>
       <c r="D23">
-        <v>22584</v>
+        <v>23207</v>
       </c>
       <c r="E23">
-        <v>22380</v>
+        <v>23060</v>
       </c>
       <c r="F23">
-        <v>1787</v>
+        <v>1628</v>
       </c>
       <c r="G23">
         <v>17204</v>
@@ -1332,10 +1332,10 @@
         <v>27601</v>
       </c>
       <c r="I23">
-        <v>32917</v>
+        <v>33554</v>
       </c>
       <c r="J23">
-        <v>32563</v>
+        <v>33199</v>
       </c>
       <c r="K23" t="s">
         <v>41</v>
@@ -1349,16 +1349,16 @@
         <v>24</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D24">
-        <v>149</v>
+        <v>260</v>
       </c>
       <c r="E24">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="F24">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="G24">
         <v>37</v>
@@ -1367,10 +1367,10 @@
         <v>300</v>
       </c>
       <c r="I24">
-        <v>25696</v>
+        <v>26071</v>
       </c>
       <c r="J24">
-        <v>25718</v>
+        <v>25946</v>
       </c>
       <c r="K24" t="s">
         <v>42</v>
@@ -1384,16 +1384,16 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D25">
-        <v>2422</v>
+        <v>2379</v>
       </c>
       <c r="E25">
-        <v>2062</v>
+        <v>1948</v>
       </c>
       <c r="F25">
-        <v>1875</v>
+        <v>1602</v>
       </c>
       <c r="G25">
         <v>204</v>
@@ -1402,10 +1402,10 @@
         <v>19362</v>
       </c>
       <c r="I25">
-        <v>38047</v>
+        <v>37898</v>
       </c>
       <c r="J25">
-        <v>37157</v>
+        <v>36734</v>
       </c>
       <c r="K25" t="s">
         <v>42</v>
@@ -1419,16 +1419,16 @@
         <v>24</v>
       </c>
       <c r="C26">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="D26">
-        <v>389</v>
+        <v>342</v>
       </c>
       <c r="E26">
         <v>342</v>
       </c>
       <c r="F26">
-        <v>306</v>
+        <v>164</v>
       </c>
       <c r="G26">
         <v>36</v>
@@ -1437,10 +1437,10 @@
         <v>1070</v>
       </c>
       <c r="I26">
-        <v>27841</v>
+        <v>28288</v>
       </c>
       <c r="J26">
-        <v>27186</v>
+        <v>27030</v>
       </c>
       <c r="K26" t="s">
         <v>42</v>
@@ -1454,16 +1454,16 @@
         <v>24</v>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D27">
-        <v>4883</v>
+        <v>3330</v>
       </c>
       <c r="E27">
-        <v>4223</v>
+        <v>3372</v>
       </c>
       <c r="F27">
-        <v>2175</v>
+        <v>1477</v>
       </c>
       <c r="G27">
         <v>2252</v>
@@ -1472,10 +1472,10 @@
         <v>8676</v>
       </c>
       <c r="I27">
-        <v>59735</v>
+        <v>54806</v>
       </c>
       <c r="J27">
-        <v>62254</v>
+        <v>56791</v>
       </c>
       <c r="K27" t="s">
         <v>42</v>
@@ -1489,16 +1489,16 @@
         <v>24</v>
       </c>
       <c r="C28">
-        <v>210</v>
+        <v>1650</v>
       </c>
       <c r="D28">
-        <v>2928</v>
+        <v>2946</v>
       </c>
       <c r="E28">
-        <v>2564</v>
+        <v>2571</v>
       </c>
       <c r="F28">
-        <v>1512</v>
+        <v>1351</v>
       </c>
       <c r="G28">
         <v>133</v>
@@ -1507,10 +1507,10 @@
         <v>11266</v>
       </c>
       <c r="I28">
-        <v>41511</v>
+        <v>41843</v>
       </c>
       <c r="J28">
-        <v>40624</v>
+        <v>41173</v>
       </c>
       <c r="K28" t="s">
         <v>42</v>
@@ -1524,16 +1524,16 @@
         <v>24</v>
       </c>
       <c r="C29">
-        <v>79</v>
+        <v>679</v>
       </c>
       <c r="D29">
-        <v>1654</v>
+        <v>1737</v>
       </c>
       <c r="E29">
-        <v>1440</v>
+        <v>1505</v>
       </c>
       <c r="F29">
-        <v>1117</v>
+        <v>898</v>
       </c>
       <c r="G29">
         <v>90</v>
@@ -1542,10 +1542,10 @@
         <v>6652</v>
       </c>
       <c r="I29">
-        <v>34571</v>
+        <v>35291</v>
       </c>
       <c r="J29">
-        <v>34003</v>
+        <v>34704</v>
       </c>
       <c r="K29" t="s">
         <v>42</v>
@@ -1559,16 +1559,16 @@
         <v>24</v>
       </c>
       <c r="C30">
-        <v>604</v>
+        <v>6028</v>
       </c>
       <c r="D30">
-        <v>6074</v>
+        <v>6027</v>
       </c>
       <c r="E30">
-        <v>5150</v>
+        <v>4994</v>
       </c>
       <c r="F30">
-        <v>3368</v>
+        <v>3306</v>
       </c>
       <c r="G30">
         <v>451</v>
@@ -1577,10 +1577,10 @@
         <v>19490</v>
       </c>
       <c r="I30">
-        <v>54497</v>
+        <v>54125</v>
       </c>
       <c r="J30">
-        <v>52711</v>
+        <v>53044</v>
       </c>
       <c r="K30" t="s">
         <v>42</v>
@@ -1594,16 +1594,16 @@
         <v>24</v>
       </c>
       <c r="C31">
-        <v>41</v>
+        <v>329</v>
       </c>
       <c r="D31">
-        <v>954</v>
+        <v>981</v>
       </c>
       <c r="E31">
-        <v>726</v>
+        <v>606</v>
       </c>
       <c r="F31">
-        <v>846</v>
+        <v>1099</v>
       </c>
       <c r="G31">
         <v>89</v>
@@ -1612,10 +1612,10 @@
         <v>4539</v>
       </c>
       <c r="I31">
-        <v>31463</v>
+        <v>31708</v>
       </c>
       <c r="J31">
-        <v>30656</v>
+        <v>31372</v>
       </c>
       <c r="K31" t="s">
         <v>42</v>
@@ -1629,16 +1629,16 @@
         <v>24</v>
       </c>
       <c r="C32">
-        <v>1071</v>
+        <v>10263</v>
       </c>
       <c r="D32">
-        <v>5675</v>
+        <v>5446</v>
       </c>
       <c r="E32">
-        <v>4837</v>
+        <v>4763</v>
       </c>
       <c r="F32">
-        <v>3809</v>
+        <v>3461</v>
       </c>
       <c r="G32">
         <v>51</v>
@@ -1647,10 +1647,10 @@
         <v>25707</v>
       </c>
       <c r="I32">
-        <v>54706</v>
+        <v>54691</v>
       </c>
       <c r="J32">
-        <v>54045</v>
+        <v>54692</v>
       </c>
       <c r="K32" t="s">
         <v>42</v>
@@ -1664,16 +1664,16 @@
         <v>24</v>
       </c>
       <c r="C33">
-        <v>486</v>
+        <v>3798</v>
       </c>
       <c r="D33">
-        <v>4180</v>
+        <v>4381</v>
       </c>
       <c r="E33">
-        <v>3489</v>
+        <v>3359</v>
       </c>
       <c r="F33">
-        <v>2758</v>
+        <v>3271</v>
       </c>
       <c r="G33">
         <v>119</v>
@@ -1682,10 +1682,10 @@
         <v>27070</v>
       </c>
       <c r="I33">
-        <v>45327</v>
+        <v>45575</v>
       </c>
       <c r="J33">
-        <v>44119</v>
+        <v>44557</v>
       </c>
       <c r="K33" t="s">
         <v>42</v>
@@ -1699,16 +1699,16 @@
         <v>24</v>
       </c>
       <c r="C34">
-        <v>337</v>
+        <v>3049</v>
       </c>
       <c r="D34">
-        <v>4915</v>
+        <v>4682</v>
       </c>
       <c r="E34">
-        <v>3965</v>
+        <v>3866</v>
       </c>
       <c r="F34">
-        <v>2898</v>
+        <v>2817</v>
       </c>
       <c r="G34">
         <v>410</v>
@@ -1717,10 +1717,10 @@
         <v>16835</v>
       </c>
       <c r="I34">
-        <v>48937</v>
+        <v>49434</v>
       </c>
       <c r="J34">
-        <v>47503</v>
+        <v>48253</v>
       </c>
       <c r="K34" t="s">
         <v>42</v>
@@ -1734,16 +1734,16 @@
         <v>25</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="D35">
-        <v>20146</v>
+        <v>20474</v>
       </c>
       <c r="E35">
-        <v>20429</v>
+        <v>20474</v>
       </c>
       <c r="F35">
-        <v>1058</v>
+        <v>911</v>
       </c>
       <c r="G35">
         <v>18473</v>
@@ -1752,10 +1752,10 @@
         <v>21824</v>
       </c>
       <c r="I35">
-        <v>47987</v>
+        <v>48762</v>
       </c>
       <c r="J35">
-        <v>47615</v>
+        <v>47504</v>
       </c>
       <c r="K35" t="s">
         <v>43</v>
@@ -1769,16 +1769,16 @@
         <v>25</v>
       </c>
       <c r="C36">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D36">
-        <v>28242</v>
+        <v>28672</v>
       </c>
       <c r="E36">
-        <v>27716</v>
+        <v>27473</v>
       </c>
       <c r="F36">
-        <v>3300</v>
+        <v>4549</v>
       </c>
       <c r="G36">
         <v>22061</v>
@@ -1787,10 +1787,10 @@
         <v>50736</v>
       </c>
       <c r="I36">
-        <v>66289</v>
+        <v>66570</v>
       </c>
       <c r="J36">
-        <v>64873</v>
+        <v>64207</v>
       </c>
       <c r="K36" t="s">
         <v>43</v>
@@ -1804,16 +1804,16 @@
         <v>25</v>
       </c>
       <c r="C37">
-        <v>79</v>
+        <v>679</v>
       </c>
       <c r="D37">
-        <v>26052</v>
+        <v>26549</v>
       </c>
       <c r="E37">
-        <v>25604</v>
+        <v>25517</v>
       </c>
       <c r="F37">
-        <v>2826</v>
+        <v>3487</v>
       </c>
       <c r="G37">
         <v>19186</v>
@@ -1822,10 +1822,10 @@
         <v>38939</v>
       </c>
       <c r="I37">
-        <v>60623</v>
+        <v>61840</v>
       </c>
       <c r="J37">
-        <v>59607</v>
+        <v>60221</v>
       </c>
       <c r="K37" t="s">
         <v>43</v>
@@ -1839,16 +1839,16 @@
         <v>25</v>
       </c>
       <c r="C38">
-        <v>604</v>
+        <v>6028</v>
       </c>
       <c r="D38">
-        <v>38485</v>
+        <v>38559</v>
       </c>
       <c r="E38">
-        <v>38306</v>
+        <v>38456</v>
       </c>
       <c r="F38">
-        <v>3270</v>
+        <v>3235</v>
       </c>
       <c r="G38">
         <v>29797</v>
@@ -1857,10 +1857,10 @@
         <v>57228</v>
       </c>
       <c r="I38">
-        <v>92982</v>
+        <v>92684</v>
       </c>
       <c r="J38">
-        <v>91017</v>
+        <v>91500</v>
       </c>
       <c r="K38" t="s">
         <v>43</v>
@@ -1874,16 +1874,16 @@
         <v>25</v>
       </c>
       <c r="C39">
-        <v>211</v>
+        <v>1651</v>
       </c>
       <c r="D39">
-        <v>31508</v>
+        <v>32145</v>
       </c>
       <c r="E39">
-        <v>31168</v>
+        <v>31821</v>
       </c>
       <c r="F39">
-        <v>2988</v>
+        <v>3301</v>
       </c>
       <c r="G39">
         <v>25121</v>
@@ -1892,10 +1892,10 @@
         <v>41266</v>
       </c>
       <c r="I39">
-        <v>73019</v>
+        <v>73988</v>
       </c>
       <c r="J39">
-        <v>71792</v>
+        <v>72994</v>
       </c>
       <c r="K39" t="s">
         <v>43</v>
@@ -1909,16 +1909,16 @@
         <v>25</v>
       </c>
       <c r="C40">
-        <v>337</v>
+        <v>3049</v>
       </c>
       <c r="D40">
-        <v>35771</v>
+        <v>36223</v>
       </c>
       <c r="E40">
-        <v>35524</v>
+        <v>35946</v>
       </c>
       <c r="F40">
-        <v>3434</v>
+        <v>3921</v>
       </c>
       <c r="G40">
         <v>25882</v>
@@ -1927,10 +1927,10 @@
         <v>52560</v>
       </c>
       <c r="I40">
-        <v>84708</v>
+        <v>85657</v>
       </c>
       <c r="J40">
-        <v>83027</v>
+        <v>84199</v>
       </c>
       <c r="K40" t="s">
         <v>43</v>
@@ -1944,16 +1944,16 @@
         <v>25</v>
       </c>
       <c r="C41">
-        <v>924</v>
+        <v>8892</v>
       </c>
       <c r="D41">
-        <v>38690</v>
+        <v>39107</v>
       </c>
       <c r="E41">
-        <v>39364</v>
+        <v>39691</v>
       </c>
       <c r="F41">
-        <v>6896</v>
+        <v>6903</v>
       </c>
       <c r="G41">
         <v>19256</v>
@@ -1962,10 +1962,10 @@
         <v>58988</v>
       </c>
       <c r="I41">
-        <v>93396</v>
+        <v>93798</v>
       </c>
       <c r="J41">
-        <v>93409</v>
+        <v>94383</v>
       </c>
       <c r="K41" t="s">
         <v>43</v>
@@ -1979,16 +1979,16 @@
         <v>25</v>
       </c>
       <c r="C42">
-        <v>41</v>
+        <v>329</v>
       </c>
       <c r="D42">
-        <v>23211</v>
+        <v>22953</v>
       </c>
       <c r="E42">
         <v>23249</v>
       </c>
       <c r="F42">
-        <v>1868</v>
+        <v>1832</v>
       </c>
       <c r="G42">
         <v>18737</v>
@@ -1997,10 +1997,10 @@
         <v>26892</v>
       </c>
       <c r="I42">
-        <v>54674</v>
+        <v>54661</v>
       </c>
       <c r="J42">
-        <v>53905</v>
+        <v>54621</v>
       </c>
       <c r="K42" t="s">
         <v>43</v>
@@ -2014,16 +2014,16 @@
         <v>25</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D43">
-        <v>18995</v>
+        <v>19040</v>
       </c>
       <c r="E43">
         <v>19218</v>
       </c>
       <c r="F43">
-        <v>677</v>
+        <v>828</v>
       </c>
       <c r="G43">
         <v>18206</v>
@@ -2032,10 +2032,10 @@
         <v>19884</v>
       </c>
       <c r="I43">
-        <v>44691</v>
+        <v>45111</v>
       </c>
       <c r="J43">
-        <v>44936</v>
+        <v>45164</v>
       </c>
       <c r="K43" t="s">
         <v>43</v>
@@ -2049,16 +2049,16 @@
         <v>25</v>
       </c>
       <c r="C44">
-        <v>487</v>
+        <v>3799</v>
       </c>
       <c r="D44">
-        <v>33604</v>
+        <v>33734</v>
       </c>
       <c r="E44">
-        <v>33352</v>
+        <v>33247</v>
       </c>
       <c r="F44">
-        <v>3279</v>
+        <v>3785</v>
       </c>
       <c r="G44">
         <v>24641</v>
@@ -2067,10 +2067,10 @@
         <v>58421</v>
       </c>
       <c r="I44">
-        <v>78931</v>
+        <v>79309</v>
       </c>
       <c r="J44">
-        <v>77471</v>
+        <v>77804</v>
       </c>
       <c r="K44" t="s">
         <v>43</v>
@@ -2084,16 +2084,16 @@
         <v>25</v>
       </c>
       <c r="C45">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D45">
-        <v>39447</v>
+        <v>39275</v>
       </c>
       <c r="E45">
         <v>38974</v>
       </c>
       <c r="F45">
-        <v>3286</v>
+        <v>3786</v>
       </c>
       <c r="G45">
         <v>33968</v>
@@ -2102,10 +2102,10 @@
         <v>44527</v>
       </c>
       <c r="I45">
-        <v>99182</v>
+        <v>94081</v>
       </c>
       <c r="J45">
-        <v>101228</v>
+        <v>95765</v>
       </c>
       <c r="K45" t="s">
         <v>43</v>
@@ -2119,16 +2119,16 @@
         <v>26</v>
       </c>
       <c r="C46">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="D46">
-        <v>17733</v>
+        <v>17395</v>
       </c>
       <c r="E46">
-        <v>17462</v>
+        <v>17239</v>
       </c>
       <c r="F46">
-        <v>1452</v>
+        <v>1136</v>
       </c>
       <c r="G46">
         <v>15544</v>
@@ -2137,10 +2137,10 @@
         <v>20110</v>
       </c>
       <c r="I46">
-        <v>65720</v>
+        <v>66157</v>
       </c>
       <c r="J46">
-        <v>65077</v>
+        <v>64743</v>
       </c>
       <c r="K46" t="s">
         <v>43</v>
@@ -2154,16 +2154,16 @@
         <v>26</v>
       </c>
       <c r="C47">
-        <v>173</v>
+        <v>1037</v>
       </c>
       <c r="D47">
-        <v>24274</v>
+        <v>23971</v>
       </c>
       <c r="E47">
-        <v>23757</v>
+        <v>23982</v>
       </c>
       <c r="F47">
-        <v>2869</v>
+        <v>2454</v>
       </c>
       <c r="G47">
         <v>19284</v>
@@ -2172,10 +2172,10 @@
         <v>43082</v>
       </c>
       <c r="I47">
-        <v>90563</v>
+        <v>90541</v>
       </c>
       <c r="J47">
-        <v>88630</v>
+        <v>88189</v>
       </c>
       <c r="K47" t="s">
         <v>43</v>
@@ -2189,16 +2189,16 @@
         <v>26</v>
       </c>
       <c r="C48">
-        <v>486</v>
+        <v>3774</v>
       </c>
       <c r="D48">
-        <v>27854</v>
+        <v>27878</v>
       </c>
       <c r="E48">
-        <v>27597</v>
+        <v>27393</v>
       </c>
       <c r="F48">
-        <v>2624</v>
+        <v>2644</v>
       </c>
       <c r="G48">
         <v>20656</v>
@@ -2207,10 +2207,10 @@
         <v>37967</v>
       </c>
       <c r="I48">
-        <v>106785</v>
+        <v>107187</v>
       </c>
       <c r="J48">
-        <v>105068</v>
+        <v>105197</v>
       </c>
       <c r="K48" t="s">
         <v>43</v>
@@ -2224,16 +2224,16 @@
         <v>26</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D49">
-        <v>16271</v>
+        <v>16227</v>
       </c>
       <c r="E49">
         <v>16306</v>
       </c>
       <c r="F49">
-        <v>389</v>
+        <v>536</v>
       </c>
       <c r="G49">
         <v>15676</v>
@@ -2242,10 +2242,10 @@
         <v>16769</v>
       </c>
       <c r="I49">
-        <v>60962</v>
+        <v>61338</v>
       </c>
       <c r="J49">
-        <v>61242</v>
+        <v>61470</v>
       </c>
       <c r="K49" t="s">
         <v>43</v>
@@ -2259,16 +2259,16 @@
         <v>26</v>
       </c>
       <c r="C50">
-        <v>337</v>
+        <v>3049</v>
       </c>
       <c r="D50">
-        <v>29475</v>
+        <v>29958</v>
       </c>
       <c r="E50">
-        <v>29339</v>
+        <v>29728</v>
       </c>
       <c r="F50">
-        <v>2806</v>
+        <v>3214</v>
       </c>
       <c r="G50">
         <v>22304</v>
@@ -2277,10 +2277,10 @@
         <v>42588</v>
       </c>
       <c r="I50">
-        <v>114183</v>
+        <v>115615</v>
       </c>
       <c r="J50">
-        <v>112366</v>
+        <v>113927</v>
       </c>
       <c r="K50" t="s">
         <v>43</v>
@@ -2294,16 +2294,16 @@
         <v>26</v>
       </c>
       <c r="C51">
-        <v>212</v>
+        <v>1676</v>
       </c>
       <c r="D51">
-        <v>25909</v>
+        <v>25855</v>
       </c>
       <c r="E51">
-        <v>25561</v>
+        <v>25572</v>
       </c>
       <c r="F51">
-        <v>2413</v>
+        <v>2680</v>
       </c>
       <c r="G51">
         <v>21380</v>
@@ -2312,10 +2312,10 @@
         <v>37045</v>
       </c>
       <c r="I51">
-        <v>98928</v>
+        <v>99843</v>
       </c>
       <c r="J51">
-        <v>97353</v>
+        <v>98566</v>
       </c>
       <c r="K51" t="s">
         <v>43</v>
@@ -2329,16 +2329,16 @@
         <v>26</v>
       </c>
       <c r="C52">
-        <v>606</v>
+        <v>5982</v>
       </c>
       <c r="D52">
-        <v>32523</v>
+        <v>32973</v>
       </c>
       <c r="E52">
-        <v>32256</v>
+        <v>32737</v>
       </c>
       <c r="F52">
-        <v>3555</v>
+        <v>3552</v>
       </c>
       <c r="G52">
         <v>23996</v>
@@ -2347,10 +2347,10 @@
         <v>48140</v>
       </c>
       <c r="I52">
-        <v>125505</v>
+        <v>125657</v>
       </c>
       <c r="J52">
-        <v>123273</v>
+        <v>124237</v>
       </c>
       <c r="K52" t="s">
         <v>43</v>
@@ -2364,16 +2364,16 @@
         <v>26</v>
       </c>
       <c r="C53">
-        <v>79</v>
+        <v>679</v>
       </c>
       <c r="D53">
-        <v>22576</v>
+        <v>21667</v>
       </c>
       <c r="E53">
-        <v>22233</v>
+        <v>21340</v>
       </c>
       <c r="F53">
-        <v>2258</v>
+        <v>1980</v>
       </c>
       <c r="G53">
         <v>18791</v>
@@ -2382,10 +2382,10 @@
         <v>30496</v>
       </c>
       <c r="I53">
-        <v>83199</v>
+        <v>83507</v>
       </c>
       <c r="J53">
-        <v>81840</v>
+        <v>81561</v>
       </c>
       <c r="K53" t="s">
         <v>43</v>
@@ -2399,16 +2399,16 @@
         <v>26</v>
       </c>
       <c r="C54">
-        <v>764</v>
+        <v>7268</v>
       </c>
       <c r="D54">
-        <v>33052</v>
+        <v>33970</v>
       </c>
       <c r="E54">
-        <v>33573</v>
+        <v>34210</v>
       </c>
       <c r="F54">
-        <v>6340</v>
+        <v>6441</v>
       </c>
       <c r="G54">
         <v>12001</v>
@@ -2417,10 +2417,10 @@
         <v>54573</v>
       </c>
       <c r="I54">
-        <v>126448</v>
+        <v>127768</v>
       </c>
       <c r="J54">
-        <v>126982</v>
+        <v>128593</v>
       </c>
       <c r="K54" t="s">
         <v>43</v>
@@ -2434,16 +2434,16 @@
         <v>26</v>
       </c>
       <c r="C55">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D55">
-        <v>20250</v>
+        <v>20103</v>
       </c>
       <c r="E55">
         <v>20347</v>
       </c>
       <c r="F55">
-        <v>1749</v>
+        <v>1855</v>
       </c>
       <c r="G55">
         <v>17109</v>
@@ -2452,10 +2452,10 @@
         <v>24802</v>
       </c>
       <c r="I55">
-        <v>74924</v>
+        <v>74764</v>
       </c>
       <c r="J55">
-        <v>74252</v>
+        <v>74968</v>
       </c>
       <c r="K55" t="s">
         <v>43</v>
@@ -2469,16 +2469,16 @@
         <v>26</v>
       </c>
       <c r="C56">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D56">
-        <v>34845</v>
+        <v>34364</v>
       </c>
       <c r="E56">
         <v>33800</v>
       </c>
       <c r="F56">
-        <v>4097</v>
+        <v>4115</v>
       </c>
       <c r="G56">
         <v>28463</v>
@@ -2487,10 +2487,10 @@
         <v>42574</v>
       </c>
       <c r="I56">
-        <v>134027</v>
+        <v>128445</v>
       </c>
       <c r="J56">
-        <v>135028</v>
+        <v>129565</v>
       </c>
       <c r="K56" t="s">
         <v>43</v>
@@ -2504,16 +2504,16 @@
         <v>27</v>
       </c>
       <c r="C57">
-        <v>320</v>
+        <v>2888</v>
       </c>
       <c r="D57">
-        <v>10353</v>
+        <v>9630</v>
       </c>
       <c r="E57">
-        <v>9642</v>
+        <v>8632</v>
       </c>
       <c r="F57">
-        <v>4958</v>
+        <v>4963</v>
       </c>
       <c r="G57">
         <v>1524</v>
@@ -2522,10 +2522,10 @@
         <v>32393</v>
       </c>
       <c r="I57">
-        <v>124536</v>
+        <v>125245</v>
       </c>
       <c r="J57">
-        <v>122008</v>
+        <v>122559</v>
       </c>
       <c r="K57" t="s">
         <v>44</v>
@@ -2539,16 +2539,16 @@
         <v>27</v>
       </c>
       <c r="C58">
-        <v>571</v>
+        <v>5635</v>
       </c>
       <c r="D58">
-        <v>12288</v>
+        <v>11509</v>
       </c>
       <c r="E58">
-        <v>12471</v>
+        <v>11696</v>
       </c>
       <c r="F58">
-        <v>4688</v>
+        <v>4594</v>
       </c>
       <c r="G58">
         <v>10</v>
@@ -2557,10 +2557,10 @@
         <v>36776</v>
       </c>
       <c r="I58">
-        <v>137793</v>
+        <v>137166</v>
       </c>
       <c r="J58">
-        <v>135744</v>
+        <v>135933</v>
       </c>
       <c r="K58" t="s">
         <v>44</v>
@@ -2574,16 +2574,16 @@
         <v>27</v>
       </c>
       <c r="C59">
-        <v>71</v>
+        <v>623</v>
       </c>
       <c r="D59">
-        <v>3035</v>
+        <v>2851</v>
       </c>
       <c r="E59">
-        <v>2611</v>
+        <v>1941</v>
       </c>
       <c r="F59">
-        <v>2081</v>
+        <v>2485</v>
       </c>
       <c r="G59">
         <v>22</v>
@@ -2592,10 +2592,10 @@
         <v>13732</v>
       </c>
       <c r="I59">
-        <v>86234</v>
+        <v>86358</v>
       </c>
       <c r="J59">
-        <v>84451</v>
+        <v>83502</v>
       </c>
       <c r="K59" t="s">
         <v>44</v>
@@ -2609,16 +2609,16 @@
         <v>27</v>
       </c>
       <c r="C60">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="D60">
-        <v>1768</v>
+        <v>1480</v>
       </c>
       <c r="E60">
-        <v>1696</v>
+        <v>1556</v>
       </c>
       <c r="F60">
-        <v>942</v>
+        <v>630</v>
       </c>
       <c r="G60">
         <v>34</v>
@@ -2627,10 +2627,10 @@
         <v>4470</v>
       </c>
       <c r="I60">
-        <v>76692</v>
+        <v>76244</v>
       </c>
       <c r="J60">
-        <v>75948</v>
+        <v>76524</v>
       </c>
       <c r="K60" t="s">
         <v>44</v>
@@ -2644,16 +2644,16 @@
         <v>27</v>
       </c>
       <c r="C61">
-        <v>201</v>
+        <v>1545</v>
       </c>
       <c r="D61">
-        <v>6409</v>
+        <v>6236</v>
       </c>
       <c r="E61">
-        <v>5922</v>
+        <v>5566</v>
       </c>
       <c r="F61">
-        <v>3307</v>
+        <v>3223</v>
       </c>
       <c r="G61">
         <v>34</v>
@@ -2662,10 +2662,10 @@
         <v>22038</v>
       </c>
       <c r="I61">
-        <v>105337</v>
+        <v>106079</v>
       </c>
       <c r="J61">
-        <v>103275</v>
+        <v>104132</v>
       </c>
       <c r="K61" t="s">
         <v>44</v>
@@ -2679,16 +2679,16 @@
         <v>27</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D62">
-        <v>293</v>
+        <v>607</v>
       </c>
       <c r="E62">
-        <v>75</v>
+        <v>626</v>
       </c>
       <c r="F62">
-        <v>317</v>
+        <v>136</v>
       </c>
       <c r="G62">
         <v>44</v>
@@ -2697,10 +2697,10 @@
         <v>654</v>
       </c>
       <c r="I62">
-        <v>61255</v>
+        <v>61945</v>
       </c>
       <c r="J62">
-        <v>61317</v>
+        <v>62096</v>
       </c>
       <c r="K62" t="s">
         <v>44</v>
@@ -2714,16 +2714,16 @@
         <v>27</v>
       </c>
       <c r="C63">
-        <v>165</v>
+        <v>981</v>
       </c>
       <c r="D63">
-        <v>4403</v>
+        <v>4490</v>
       </c>
       <c r="E63">
-        <v>3782</v>
+        <v>3820</v>
       </c>
       <c r="F63">
-        <v>2853</v>
+        <v>2570</v>
       </c>
       <c r="G63">
         <v>98</v>
@@ -2732,10 +2732,10 @@
         <v>18257</v>
       </c>
       <c r="I63">
-        <v>94966</v>
+        <v>95031</v>
       </c>
       <c r="J63">
-        <v>92412</v>
+        <v>92009</v>
       </c>
       <c r="K63" t="s">
         <v>44</v>
@@ -2749,16 +2749,16 @@
         <v>27</v>
       </c>
       <c r="C64">
-        <v>677</v>
+        <v>6341</v>
       </c>
       <c r="D64">
-        <v>10252</v>
+        <v>10221</v>
       </c>
       <c r="E64">
-        <v>9823</v>
+        <v>9756</v>
       </c>
       <c r="F64">
-        <v>6152</v>
+        <v>5909</v>
       </c>
       <c r="G64">
         <v>9</v>
@@ -2767,10 +2767,10 @@
         <v>48204</v>
       </c>
       <c r="I64">
-        <v>136700</v>
+        <v>137989</v>
       </c>
       <c r="J64">
-        <v>136805</v>
+        <v>138349</v>
       </c>
       <c r="K64" t="s">
         <v>44</v>
@@ -2784,16 +2784,16 @@
         <v>27</v>
       </c>
       <c r="C65">
-        <v>463</v>
+        <v>3631</v>
       </c>
       <c r="D65">
-        <v>8703</v>
+        <v>8764</v>
       </c>
       <c r="E65">
-        <v>8264</v>
+        <v>8240</v>
       </c>
       <c r="F65">
-        <v>4073</v>
+        <v>4088</v>
       </c>
       <c r="G65">
         <v>96</v>
@@ -2802,10 +2802,10 @@
         <v>25227</v>
       </c>
       <c r="I65">
-        <v>115488</v>
+        <v>115951</v>
       </c>
       <c r="J65">
-        <v>113332</v>
+        <v>113437</v>
       </c>
       <c r="K65" t="s">
         <v>44</v>
@@ -2819,16 +2819,16 @@
         <v>27</v>
       </c>
       <c r="C66">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D66">
-        <v>9357</v>
+        <v>8229</v>
       </c>
       <c r="E66">
         <v>9681</v>
       </c>
       <c r="F66">
-        <v>4907</v>
+        <v>3008</v>
       </c>
       <c r="G66">
         <v>3159</v>
@@ -2837,10 +2837,10 @@
         <v>19643</v>
       </c>
       <c r="I66">
-        <v>143384</v>
+        <v>136674</v>
       </c>
       <c r="J66">
-        <v>144709</v>
+        <v>139246</v>
       </c>
       <c r="K66" t="s">
         <v>44</v>
@@ -2854,16 +2854,16 @@
         <v>27</v>
       </c>
       <c r="C67">
-        <v>16</v>
+        <v>184</v>
       </c>
       <c r="D67">
-        <v>1062</v>
+        <v>903</v>
       </c>
       <c r="E67">
-        <v>1098</v>
+        <v>999</v>
       </c>
       <c r="F67">
-        <v>788</v>
+        <v>649</v>
       </c>
       <c r="G67">
         <v>9</v>
@@ -2872,10 +2872,10 @@
         <v>2033</v>
       </c>
       <c r="I67">
-        <v>66782</v>
+        <v>67060</v>
       </c>
       <c r="J67">
-        <v>66175</v>
+        <v>65742</v>
       </c>
       <c r="K67" t="s">
         <v>44</v>
@@ -2889,16 +2889,16 @@
         <v>28</v>
       </c>
       <c r="C68">
-        <v>203</v>
+        <v>1547</v>
       </c>
       <c r="D68">
-        <v>40053</v>
+        <v>40413</v>
       </c>
       <c r="E68">
-        <v>39701</v>
+        <v>40042</v>
       </c>
       <c r="F68">
-        <v>3864</v>
+        <v>3752</v>
       </c>
       <c r="G68">
         <v>32910</v>
@@ -2907,10 +2907,10 @@
         <v>51338</v>
       </c>
       <c r="I68">
-        <v>145390</v>
+        <v>146492</v>
       </c>
       <c r="J68">
-        <v>142976</v>
+        <v>144174</v>
       </c>
       <c r="K68" t="s">
         <v>45</v>
@@ -2924,16 +2924,16 @@
         <v>28</v>
       </c>
       <c r="C69">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="D69">
-        <v>29346</v>
+        <v>28681</v>
       </c>
       <c r="E69">
-        <v>29461</v>
+        <v>27547</v>
       </c>
       <c r="F69">
-        <v>2463</v>
+        <v>3138</v>
       </c>
       <c r="G69">
         <v>25117</v>
@@ -2942,10 +2942,10 @@
         <v>37127</v>
       </c>
       <c r="I69">
-        <v>106038</v>
+        <v>104925</v>
       </c>
       <c r="J69">
-        <v>105409</v>
+        <v>104071</v>
       </c>
       <c r="K69" t="s">
         <v>45</v>
@@ -2959,16 +2959,16 @@
         <v>28</v>
       </c>
       <c r="C70">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D70">
-        <v>25610</v>
+        <v>23938</v>
       </c>
       <c r="E70">
-        <v>25142</v>
+        <v>23799</v>
       </c>
       <c r="F70">
-        <v>2016</v>
+        <v>781</v>
       </c>
       <c r="G70">
         <v>23728</v>
@@ -2977,10 +2977,10 @@
         <v>28220</v>
       </c>
       <c r="I70">
-        <v>86865</v>
+        <v>85883</v>
       </c>
       <c r="J70">
-        <v>86459</v>
+        <v>85895</v>
       </c>
       <c r="K70" t="s">
         <v>45</v>
@@ -2994,16 +2994,16 @@
         <v>28</v>
       </c>
       <c r="C71">
-        <v>466</v>
+        <v>3586</v>
       </c>
       <c r="D71">
-        <v>43581</v>
+        <v>43703</v>
       </c>
       <c r="E71">
-        <v>43166</v>
+        <v>43528</v>
       </c>
       <c r="F71">
-        <v>4767</v>
+        <v>4375</v>
       </c>
       <c r="G71">
         <v>32320</v>
@@ -3012,10 +3012,10 @@
         <v>62161</v>
       </c>
       <c r="I71">
-        <v>159069</v>
+        <v>159654</v>
       </c>
       <c r="J71">
-        <v>156498</v>
+        <v>156965</v>
       </c>
       <c r="K71" t="s">
         <v>45</v>
@@ -3029,16 +3029,16 @@
         <v>28</v>
       </c>
       <c r="C72">
-        <v>320</v>
+        <v>2864</v>
       </c>
       <c r="D72">
-        <v>46073</v>
+        <v>46725</v>
       </c>
       <c r="E72">
-        <v>45926</v>
+        <v>47388</v>
       </c>
       <c r="F72">
-        <v>5068</v>
+        <v>5411</v>
       </c>
       <c r="G72">
         <v>32861</v>
@@ -3047,10 +3047,10 @@
         <v>63679</v>
       </c>
       <c r="I72">
-        <v>170609</v>
+        <v>171970</v>
       </c>
       <c r="J72">
-        <v>167934</v>
+        <v>169947</v>
       </c>
       <c r="K72" t="s">
         <v>45</v>
@@ -3064,16 +3064,16 @@
         <v>28</v>
       </c>
       <c r="C73">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D73">
-        <v>49201</v>
+        <v>49399</v>
       </c>
       <c r="E73">
         <v>49620</v>
       </c>
       <c r="F73">
-        <v>4690</v>
+        <v>2351</v>
       </c>
       <c r="G73">
         <v>38540</v>
@@ -3082,10 +3082,10 @@
         <v>57491</v>
       </c>
       <c r="I73">
-        <v>192585</v>
+        <v>186073</v>
       </c>
       <c r="J73">
-        <v>194329</v>
+        <v>188866</v>
       </c>
       <c r="K73" t="s">
         <v>45</v>
@@ -3099,16 +3099,16 @@
         <v>28</v>
       </c>
       <c r="C74">
-        <v>17</v>
+        <v>185</v>
       </c>
       <c r="D74">
-        <v>26754</v>
+        <v>26383</v>
       </c>
       <c r="E74">
-        <v>26681</v>
+        <v>26563</v>
       </c>
       <c r="F74">
-        <v>1114</v>
+        <v>1020</v>
       </c>
       <c r="G74">
         <v>25057</v>
@@ -3117,10 +3117,10 @@
         <v>28679</v>
       </c>
       <c r="I74">
-        <v>93536</v>
+        <v>93443</v>
       </c>
       <c r="J74">
-        <v>92856</v>
+        <v>92305</v>
       </c>
       <c r="K74" t="s">
         <v>45</v>
@@ -3134,16 +3134,16 @@
         <v>28</v>
       </c>
       <c r="C75">
-        <v>577</v>
+        <v>5737</v>
       </c>
       <c r="D75">
-        <v>47335</v>
+        <v>47479</v>
       </c>
       <c r="E75">
-        <v>47092</v>
+        <v>47520</v>
       </c>
       <c r="F75">
-        <v>4244</v>
+        <v>4373</v>
       </c>
       <c r="G75">
         <v>32999</v>
@@ -3152,10 +3152,10 @@
         <v>62533</v>
       </c>
       <c r="I75">
-        <v>185128</v>
+        <v>184645</v>
       </c>
       <c r="J75">
-        <v>182836</v>
+        <v>183453</v>
       </c>
       <c r="K75" t="s">
         <v>45</v>
@@ -3169,16 +3169,16 @@
         <v>28</v>
       </c>
       <c r="C76">
-        <v>586</v>
+        <v>5650</v>
       </c>
       <c r="D76">
-        <v>47692</v>
+        <v>48229</v>
       </c>
       <c r="E76">
-        <v>48564</v>
+        <v>49080</v>
       </c>
       <c r="F76">
-        <v>7294</v>
+        <v>6779</v>
       </c>
       <c r="G76">
         <v>25583</v>
@@ -3187,10 +3187,10 @@
         <v>72257</v>
       </c>
       <c r="I76">
-        <v>184392</v>
+        <v>186218</v>
       </c>
       <c r="J76">
-        <v>185369</v>
+        <v>187429</v>
       </c>
       <c r="K76" t="s">
         <v>45</v>
@@ -3204,16 +3204,16 @@
         <v>28</v>
       </c>
       <c r="C77">
-        <v>71</v>
+        <v>623</v>
       </c>
       <c r="D77">
-        <v>32478</v>
+        <v>31700</v>
       </c>
       <c r="E77">
-        <v>32042</v>
+        <v>31419</v>
       </c>
       <c r="F77">
-        <v>2145</v>
+        <v>1832</v>
       </c>
       <c r="G77">
         <v>27600</v>
@@ -3222,10 +3222,10 @@
         <v>38229</v>
       </c>
       <c r="I77">
-        <v>118712</v>
+        <v>118058</v>
       </c>
       <c r="J77">
-        <v>116493</v>
+        <v>114921</v>
       </c>
       <c r="K77" t="s">
         <v>45</v>
@@ -3239,16 +3239,16 @@
         <v>28</v>
       </c>
       <c r="C78">
-        <v>167</v>
+        <v>983</v>
       </c>
       <c r="D78">
-        <v>35625</v>
+        <v>35356</v>
       </c>
       <c r="E78">
-        <v>35209</v>
+        <v>35111</v>
       </c>
       <c r="F78">
-        <v>3326</v>
+        <v>3251</v>
       </c>
       <c r="G78">
         <v>27957</v>
@@ -3257,10 +3257,10 @@
         <v>49880</v>
       </c>
       <c r="I78">
-        <v>130591</v>
+        <v>130387</v>
       </c>
       <c r="J78">
-        <v>127621</v>
+        <v>127120</v>
       </c>
       <c r="K78" t="s">
         <v>45</v>
@@ -3274,16 +3274,16 @@
         <v>29</v>
       </c>
       <c r="C79">
-        <v>604</v>
+        <v>5980</v>
       </c>
       <c r="D79">
-        <v>10593</v>
+        <v>10351</v>
       </c>
       <c r="E79">
-        <v>10562</v>
+        <v>10200</v>
       </c>
       <c r="F79">
-        <v>4319</v>
+        <v>4297</v>
       </c>
       <c r="G79">
         <v>42</v>
@@ -3292,10 +3292,10 @@
         <v>26810</v>
       </c>
       <c r="I79">
-        <v>195721</v>
+        <v>194996</v>
       </c>
       <c r="J79">
-        <v>193398</v>
+        <v>193653</v>
       </c>
       <c r="K79" t="s">
         <v>46</v>
@@ -3309,16 +3309,16 @@
         <v>29</v>
       </c>
       <c r="C80">
-        <v>487</v>
+        <v>3703</v>
       </c>
       <c r="D80">
-        <v>9843</v>
+        <v>9425</v>
       </c>
       <c r="E80">
-        <v>9182</v>
+        <v>8589</v>
       </c>
       <c r="F80">
-        <v>5056</v>
+        <v>6091</v>
       </c>
       <c r="G80">
         <v>1612</v>
@@ -3327,10 +3327,10 @@
         <v>65211</v>
       </c>
       <c r="I80">
-        <v>168912</v>
+        <v>169079</v>
       </c>
       <c r="J80">
-        <v>165680</v>
+        <v>165554</v>
       </c>
       <c r="K80" t="s">
         <v>46</v>
@@ -3344,16 +3344,16 @@
         <v>29</v>
       </c>
       <c r="C81">
-        <v>80</v>
+        <v>680</v>
       </c>
       <c r="D81">
-        <v>6198</v>
+        <v>6525</v>
       </c>
       <c r="E81">
-        <v>5827</v>
+        <v>5687</v>
       </c>
       <c r="F81">
-        <v>3436</v>
+        <v>3736</v>
       </c>
       <c r="G81">
         <v>726</v>
@@ -3362,10 +3362,10 @@
         <v>14141</v>
       </c>
       <c r="I81">
-        <v>124910</v>
+        <v>124583</v>
       </c>
       <c r="J81">
-        <v>122320</v>
+        <v>120608</v>
       </c>
       <c r="K81" t="s">
         <v>46</v>
@@ -3379,16 +3379,16 @@
         <v>29</v>
       </c>
       <c r="C82">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D82">
-        <v>481</v>
+        <v>1100</v>
       </c>
       <c r="E82">
-        <v>41</v>
+        <v>517</v>
       </c>
       <c r="F82">
-        <v>774</v>
+        <v>688</v>
       </c>
       <c r="G82">
         <v>11</v>
@@ -3397,10 +3397,10 @@
         <v>1812</v>
       </c>
       <c r="I82">
-        <v>87346</v>
+        <v>86983</v>
       </c>
       <c r="J82">
-        <v>86500</v>
+        <v>86412</v>
       </c>
       <c r="K82" t="s">
         <v>46</v>
@@ -3414,16 +3414,16 @@
         <v>29</v>
       </c>
       <c r="C83">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D83">
-        <v>11070</v>
+        <v>9594</v>
       </c>
       <c r="E83">
         <v>8700</v>
       </c>
       <c r="F83">
-        <v>5780</v>
+        <v>3202</v>
       </c>
       <c r="G83">
         <v>4056</v>
@@ -3432,10 +3432,10 @@
         <v>24590</v>
       </c>
       <c r="I83">
-        <v>203655</v>
+        <v>195667</v>
       </c>
       <c r="J83">
-        <v>203029</v>
+        <v>197566</v>
       </c>
       <c r="K83" t="s">
         <v>46</v>
@@ -3449,16 +3449,16 @@
         <v>29</v>
       </c>
       <c r="C84">
-        <v>212</v>
+        <v>1652</v>
       </c>
       <c r="D84">
-        <v>10116</v>
+        <v>9565</v>
       </c>
       <c r="E84">
-        <v>9912</v>
+        <v>9557</v>
       </c>
       <c r="F84">
-        <v>4310</v>
+        <v>4097</v>
       </c>
       <c r="G84">
         <v>1945</v>
@@ -3467,10 +3467,10 @@
         <v>26967</v>
       </c>
       <c r="I84">
-        <v>155506</v>
+        <v>156057</v>
       </c>
       <c r="J84">
-        <v>152888</v>
+        <v>153731</v>
       </c>
       <c r="K84" t="s">
         <v>46</v>
@@ -3484,16 +3484,16 @@
         <v>29</v>
       </c>
       <c r="C85">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D85">
-        <v>9491</v>
+        <v>8470</v>
       </c>
       <c r="E85">
-        <v>8726</v>
+        <v>8623</v>
       </c>
       <c r="F85">
-        <v>4713</v>
+        <v>4133</v>
       </c>
       <c r="G85">
         <v>739</v>
@@ -3502,10 +3502,10 @@
         <v>27042</v>
       </c>
       <c r="I85">
-        <v>140082</v>
+        <v>138857</v>
       </c>
       <c r="J85">
-        <v>136347</v>
+        <v>135743</v>
       </c>
       <c r="K85" t="s">
         <v>46</v>
@@ -3519,16 +3519,16 @@
         <v>29</v>
       </c>
       <c r="C86">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D86">
-        <v>769</v>
+        <v>906</v>
       </c>
       <c r="E86">
-        <v>656</v>
+        <v>763</v>
       </c>
       <c r="F86">
-        <v>854</v>
+        <v>1018</v>
       </c>
       <c r="G86">
         <v>16</v>
@@ -3537,10 +3537,10 @@
         <v>3171</v>
       </c>
       <c r="I86">
-        <v>94305</v>
+        <v>94349</v>
       </c>
       <c r="J86">
-        <v>93512</v>
+        <v>93068</v>
       </c>
       <c r="K86" t="s">
         <v>46</v>
@@ -3554,16 +3554,16 @@
         <v>29</v>
       </c>
       <c r="C87">
-        <v>601</v>
+        <v>5857</v>
       </c>
       <c r="D87">
-        <v>11339</v>
+        <v>11085</v>
       </c>
       <c r="E87">
-        <v>11174</v>
+        <v>10935</v>
       </c>
       <c r="F87">
-        <v>5217</v>
+        <v>5063</v>
       </c>
       <c r="G87">
         <v>40</v>
@@ -3572,10 +3572,10 @@
         <v>41633</v>
       </c>
       <c r="I87">
-        <v>195731</v>
+        <v>197303</v>
       </c>
       <c r="J87">
-        <v>196543</v>
+        <v>198364</v>
       </c>
       <c r="K87" t="s">
         <v>46</v>
@@ -3589,16 +3589,16 @@
         <v>29</v>
       </c>
       <c r="C88">
-        <v>330</v>
+        <v>2922</v>
       </c>
       <c r="D88">
-        <v>9391</v>
+        <v>8588</v>
       </c>
       <c r="E88">
-        <v>9132</v>
+        <v>8086</v>
       </c>
       <c r="F88">
-        <v>4695</v>
+        <v>4652</v>
       </c>
       <c r="G88">
         <v>65</v>
@@ -3607,10 +3607,10 @@
         <v>30860</v>
       </c>
       <c r="I88">
-        <v>180000</v>
+        <v>180558</v>
       </c>
       <c r="J88">
-        <v>177066</v>
+        <v>178033</v>
       </c>
       <c r="K88" t="s">
         <v>46</v>
@@ -3624,16 +3624,16 @@
         <v>29</v>
       </c>
       <c r="C89">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D89">
-        <v>3227</v>
+        <v>2510</v>
       </c>
       <c r="E89">
         <v>2347</v>
       </c>
       <c r="F89">
-        <v>2887</v>
+        <v>2167</v>
       </c>
       <c r="G89">
         <v>27</v>
@@ -3642,10 +3642,10 @@
         <v>14815</v>
       </c>
       <c r="I89">
-        <v>109265</v>
+        <v>107435</v>
       </c>
       <c r="J89">
-        <v>107756</v>
+        <v>106418</v>
       </c>
       <c r="K89" t="s">
         <v>46</v>
@@ -3659,16 +3659,16 @@
         <v>30</v>
       </c>
       <c r="C90">
-        <v>488</v>
+        <v>3728</v>
       </c>
       <c r="D90">
-        <v>34184</v>
+        <v>34903</v>
       </c>
       <c r="E90">
-        <v>33976</v>
+        <v>34392</v>
       </c>
       <c r="F90">
-        <v>3173</v>
+        <v>3236</v>
       </c>
       <c r="G90">
         <v>25684</v>
@@ -3677,10 +3677,10 @@
         <v>47342</v>
       </c>
       <c r="I90">
-        <v>203096</v>
+        <v>203982</v>
       </c>
       <c r="J90">
-        <v>199656</v>
+        <v>199946</v>
       </c>
       <c r="K90" t="s">
         <v>47</v>
@@ -3694,16 +3694,16 @@
         <v>30</v>
       </c>
       <c r="C91">
-        <v>42</v>
+        <v>306</v>
       </c>
       <c r="D91">
-        <v>28463</v>
+        <v>27753</v>
       </c>
       <c r="E91">
-        <v>28376</v>
+        <v>27561</v>
       </c>
       <c r="F91">
-        <v>2158</v>
+        <v>1586</v>
       </c>
       <c r="G91">
         <v>24211</v>
@@ -3712,10 +3712,10 @@
         <v>35466</v>
       </c>
       <c r="I91">
-        <v>137728</v>
+        <v>135188</v>
       </c>
       <c r="J91">
-        <v>136132</v>
+        <v>133979</v>
       </c>
       <c r="K91" t="s">
         <v>47</v>
@@ -3729,16 +3729,16 @@
         <v>30</v>
       </c>
       <c r="C92">
-        <v>331</v>
+        <v>2947</v>
       </c>
       <c r="D92">
-        <v>37602</v>
+        <v>38925</v>
       </c>
       <c r="E92">
-        <v>36961</v>
+        <v>38183</v>
       </c>
       <c r="F92">
-        <v>4217</v>
+        <v>4225</v>
       </c>
       <c r="G92">
         <v>28969</v>
@@ -3747,10 +3747,10 @@
         <v>51729</v>
       </c>
       <c r="I92">
-        <v>217602</v>
+        <v>219483</v>
       </c>
       <c r="J92">
-        <v>214027</v>
+        <v>216216</v>
       </c>
       <c r="K92" t="s">
         <v>47</v>
@@ -3764,16 +3764,16 @@
         <v>30</v>
       </c>
       <c r="C93">
-        <v>603</v>
+        <v>5979</v>
       </c>
       <c r="D93">
-        <v>43049</v>
+        <v>44253</v>
       </c>
       <c r="E93">
-        <v>42814</v>
+        <v>44148</v>
       </c>
       <c r="F93">
-        <v>5410</v>
+        <v>5252</v>
       </c>
       <c r="G93">
         <v>29600</v>
@@ -3782,10 +3782,10 @@
         <v>82670</v>
       </c>
       <c r="I93">
-        <v>238770</v>
+        <v>239249</v>
       </c>
       <c r="J93">
-        <v>236212</v>
+        <v>237801</v>
       </c>
       <c r="K93" t="s">
         <v>47</v>
@@ -3799,16 +3799,16 @@
         <v>30</v>
       </c>
       <c r="C94">
-        <v>534</v>
+        <v>4974</v>
       </c>
       <c r="D94">
-        <v>43745</v>
+        <v>44837</v>
       </c>
       <c r="E94">
-        <v>44327</v>
+        <v>45414</v>
       </c>
       <c r="F94">
-        <v>7593</v>
+        <v>7171</v>
       </c>
       <c r="G94">
         <v>22216</v>
@@ -3817,10 +3817,10 @@
         <v>80739</v>
       </c>
       <c r="I94">
-        <v>239476</v>
+        <v>242140</v>
       </c>
       <c r="J94">
-        <v>240870</v>
+        <v>243778</v>
       </c>
       <c r="K94" t="s">
         <v>47</v>
@@ -3834,16 +3834,16 @@
         <v>30</v>
       </c>
       <c r="C95">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D95">
-        <v>24612</v>
+        <v>25693</v>
       </c>
       <c r="E95">
-        <v>24261</v>
+        <v>23889</v>
       </c>
       <c r="F95">
-        <v>3192</v>
+        <v>4067</v>
       </c>
       <c r="G95">
         <v>20859</v>
@@ -3852,10 +3852,10 @@
         <v>35567</v>
       </c>
       <c r="I95">
-        <v>118917</v>
+        <v>120042</v>
       </c>
       <c r="J95">
-        <v>117773</v>
+        <v>116957</v>
       </c>
       <c r="K95" t="s">
         <v>47</v>
@@ -3869,16 +3869,16 @@
         <v>30</v>
       </c>
       <c r="C96">
-        <v>80</v>
+        <v>680</v>
       </c>
       <c r="D96">
-        <v>31100</v>
+        <v>31341</v>
       </c>
       <c r="E96">
-        <v>30876</v>
+        <v>31769</v>
       </c>
       <c r="F96">
-        <v>2757</v>
+        <v>3269</v>
       </c>
       <c r="G96">
         <v>25424</v>
@@ -3887,10 +3887,10 @@
         <v>38322</v>
       </c>
       <c r="I96">
-        <v>156010</v>
+        <v>155924</v>
       </c>
       <c r="J96">
-        <v>153196</v>
+        <v>152377</v>
       </c>
       <c r="K96" t="s">
         <v>47</v>
@@ -3904,16 +3904,16 @@
         <v>30</v>
       </c>
       <c r="C97">
-        <v>211</v>
+        <v>1651</v>
       </c>
       <c r="D97">
-        <v>32541</v>
+        <v>33196</v>
       </c>
       <c r="E97">
-        <v>32288</v>
+        <v>33039</v>
       </c>
       <c r="F97">
-        <v>2782</v>
+        <v>2556</v>
       </c>
       <c r="G97">
         <v>25402</v>
@@ -3922,10 +3922,10 @@
         <v>40777</v>
       </c>
       <c r="I97">
-        <v>188047</v>
+        <v>189253</v>
       </c>
       <c r="J97">
-        <v>185176</v>
+        <v>186770</v>
       </c>
       <c r="K97" t="s">
         <v>47</v>
@@ -3939,16 +3939,16 @@
         <v>30</v>
       </c>
       <c r="C98">
-        <v>173</v>
+        <v>1037</v>
       </c>
       <c r="D98">
-        <v>31884</v>
+        <v>32313</v>
       </c>
       <c r="E98">
-        <v>31598</v>
+        <v>32059</v>
       </c>
       <c r="F98">
-        <v>3321</v>
+        <v>3310</v>
       </c>
       <c r="G98">
         <v>23777</v>
@@ -3957,10 +3957,10 @@
         <v>42262</v>
       </c>
       <c r="I98">
-        <v>171966</v>
+        <v>171170</v>
       </c>
       <c r="J98">
-        <v>167945</v>
+        <v>167802</v>
       </c>
       <c r="K98" t="s">
         <v>47</v>
@@ -3974,16 +3974,16 @@
         <v>30</v>
       </c>
       <c r="C99">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D99">
-        <v>45226</v>
+        <v>47507</v>
       </c>
       <c r="E99">
-        <v>46020</v>
+        <v>46164</v>
       </c>
       <c r="F99">
-        <v>4158</v>
+        <v>3109</v>
       </c>
       <c r="G99">
         <v>38466</v>
@@ -3992,10 +3992,10 @@
         <v>53609</v>
       </c>
       <c r="I99">
-        <v>248881</v>
+        <v>243174</v>
       </c>
       <c r="J99">
-        <v>249049</v>
+        <v>243730</v>
       </c>
       <c r="K99" t="s">
         <v>47</v>
@@ -4009,16 +4009,16 @@
         <v>30</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D100">
-        <v>21841</v>
+        <v>20184</v>
       </c>
       <c r="E100">
-        <v>23020</v>
+        <v>20706</v>
       </c>
       <c r="F100">
-        <v>1741</v>
+        <v>985</v>
       </c>
       <c r="G100">
         <v>19316</v>
@@ -4027,10 +4027,10 @@
         <v>23098</v>
       </c>
       <c r="I100">
-        <v>109187</v>
+        <v>107167</v>
       </c>
       <c r="J100">
-        <v>109520</v>
+        <v>107118</v>
       </c>
       <c r="K100" t="s">
         <v>47</v>
@@ -4044,16 +4044,16 @@
         <v>31</v>
       </c>
       <c r="C101">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D101">
-        <v>16768</v>
+        <v>16567</v>
       </c>
       <c r="E101">
-        <v>16036</v>
+        <v>14336</v>
       </c>
       <c r="F101">
-        <v>4285</v>
+        <v>3346</v>
       </c>
       <c r="G101">
         <v>11580</v>
@@ -4062,10 +4062,10 @@
         <v>30502</v>
       </c>
       <c r="I101">
-        <v>135685</v>
+        <v>136609</v>
       </c>
       <c r="J101">
-        <v>133809</v>
+        <v>131293</v>
       </c>
       <c r="K101" t="s">
         <v>47</v>
@@ -4079,16 +4079,16 @@
         <v>31</v>
       </c>
       <c r="C102">
-        <v>80</v>
+        <v>680</v>
       </c>
       <c r="D102">
-        <v>19683</v>
+        <v>18375</v>
       </c>
       <c r="E102">
-        <v>18988</v>
+        <v>18185</v>
       </c>
       <c r="F102">
-        <v>2860</v>
+        <v>1936</v>
       </c>
       <c r="G102">
         <v>15195</v>
@@ -4097,10 +4097,10 @@
         <v>32435</v>
       </c>
       <c r="I102">
-        <v>175693</v>
+        <v>174299</v>
       </c>
       <c r="J102">
-        <v>172184</v>
+        <v>170562</v>
       </c>
       <c r="K102" t="s">
         <v>47</v>
@@ -4114,16 +4114,16 @@
         <v>31</v>
       </c>
       <c r="C103">
-        <v>337</v>
+        <v>3025</v>
       </c>
       <c r="D103">
-        <v>30535</v>
+        <v>31184</v>
       </c>
       <c r="E103">
-        <v>30205</v>
+        <v>30558</v>
       </c>
       <c r="F103">
-        <v>4134</v>
+        <v>4631</v>
       </c>
       <c r="G103">
         <v>19662</v>
@@ -4132,10 +4132,10 @@
         <v>47538</v>
       </c>
       <c r="I103">
-        <v>248137</v>
+        <v>250667</v>
       </c>
       <c r="J103">
-        <v>244232</v>
+        <v>246774</v>
       </c>
       <c r="K103" t="s">
         <v>47</v>
@@ -4149,16 +4149,16 @@
         <v>31</v>
       </c>
       <c r="C104">
-        <v>434</v>
+        <v>3698</v>
       </c>
       <c r="D104">
-        <v>29249</v>
+        <v>29900</v>
       </c>
       <c r="E104">
-        <v>28746</v>
+        <v>29529</v>
       </c>
       <c r="F104">
-        <v>5838</v>
+        <v>5972</v>
       </c>
       <c r="G104">
         <v>14047</v>
@@ -4167,10 +4167,10 @@
         <v>61311</v>
       </c>
       <c r="I104">
-        <v>268725</v>
+        <v>272040</v>
       </c>
       <c r="J104">
-        <v>269616</v>
+        <v>273307</v>
       </c>
       <c r="K104" t="s">
         <v>47</v>
@@ -4184,16 +4184,16 @@
         <v>31</v>
       </c>
       <c r="C105">
-        <v>42</v>
+        <v>306</v>
       </c>
       <c r="D105">
-        <v>19766</v>
+        <v>19141</v>
       </c>
       <c r="E105">
-        <v>19595</v>
+        <v>18584</v>
       </c>
       <c r="F105">
-        <v>2697</v>
+        <v>2025</v>
       </c>
       <c r="G105">
         <v>15748</v>
@@ -4202,10 +4202,10 @@
         <v>29785</v>
       </c>
       <c r="I105">
-        <v>157494</v>
+        <v>154329</v>
       </c>
       <c r="J105">
-        <v>155727</v>
+        <v>152563</v>
       </c>
       <c r="K105" t="s">
         <v>47</v>
@@ -4219,16 +4219,16 @@
         <v>31</v>
       </c>
       <c r="C106">
-        <v>494</v>
+        <v>3806</v>
       </c>
       <c r="D106">
-        <v>26380</v>
+        <v>26686</v>
       </c>
       <c r="E106">
-        <v>25898</v>
+        <v>26019</v>
       </c>
       <c r="F106">
-        <v>4002</v>
+        <v>4042</v>
       </c>
       <c r="G106">
         <v>18403</v>
@@ -4237,10 +4237,10 @@
         <v>40014</v>
       </c>
       <c r="I106">
-        <v>229476</v>
+        <v>230668</v>
       </c>
       <c r="J106">
-        <v>225554</v>
+        <v>225965</v>
       </c>
       <c r="K106" t="s">
         <v>47</v>
@@ -4254,16 +4254,16 @@
         <v>31</v>
       </c>
       <c r="C107">
-        <v>608</v>
+        <v>6032</v>
       </c>
       <c r="D107">
-        <v>30148</v>
+        <v>30003</v>
       </c>
       <c r="E107">
-        <v>30093</v>
+        <v>29821</v>
       </c>
       <c r="F107">
-        <v>4333</v>
+        <v>4285</v>
       </c>
       <c r="G107">
         <v>21070</v>
@@ -4272,10 +4272,10 @@
         <v>46906</v>
       </c>
       <c r="I107">
-        <v>268918</v>
+        <v>269252</v>
       </c>
       <c r="J107">
-        <v>266305</v>
+        <v>267622</v>
       </c>
       <c r="K107" t="s">
         <v>47</v>
@@ -4289,16 +4289,16 @@
         <v>31</v>
       </c>
       <c r="C108">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D108">
-        <v>20036</v>
+        <v>19898</v>
       </c>
       <c r="E108">
-        <v>19817</v>
+        <v>19608</v>
       </c>
       <c r="F108">
-        <v>2144</v>
+        <v>1944</v>
       </c>
       <c r="G108">
         <v>14640</v>
@@ -4307,10 +4307,10 @@
         <v>26098</v>
       </c>
       <c r="I108">
-        <v>192002</v>
+        <v>191068</v>
       </c>
       <c r="J108">
-        <v>187762</v>
+        <v>187410</v>
       </c>
       <c r="K108" t="s">
         <v>47</v>
@@ -4324,16 +4324,16 @@
         <v>31</v>
       </c>
       <c r="C109">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D109">
-        <v>29412</v>
+        <v>31461</v>
       </c>
       <c r="E109">
-        <v>29117</v>
+        <v>30020</v>
       </c>
       <c r="F109">
-        <v>3229</v>
+        <v>2764</v>
       </c>
       <c r="G109">
         <v>23826</v>
@@ -4342,10 +4342,10 @@
         <v>37106</v>
       </c>
       <c r="I109">
-        <v>278293</v>
+        <v>274635</v>
       </c>
       <c r="J109">
-        <v>278166</v>
+        <v>273750</v>
       </c>
       <c r="K109" t="s">
         <v>47</v>
@@ -4359,16 +4359,16 @@
         <v>31</v>
       </c>
       <c r="C110">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D110">
-        <v>12900</v>
+        <v>12398</v>
       </c>
       <c r="E110">
-        <v>12587</v>
+        <v>12355</v>
       </c>
       <c r="F110">
-        <v>658</v>
+        <v>245</v>
       </c>
       <c r="G110">
         <v>12337</v>
@@ -4377,10 +4377,10 @@
         <v>13684</v>
       </c>
       <c r="I110">
-        <v>122087</v>
+        <v>119565</v>
       </c>
       <c r="J110">
-        <v>122107</v>
+        <v>119473</v>
       </c>
       <c r="K110" t="s">
         <v>47</v>
@@ -4394,16 +4394,16 @@
         <v>31</v>
       </c>
       <c r="C111">
-        <v>212</v>
+        <v>1652</v>
       </c>
       <c r="D111">
-        <v>22272</v>
+        <v>22472</v>
       </c>
       <c r="E111">
-        <v>21874</v>
+        <v>22285</v>
       </c>
       <c r="F111">
-        <v>2626</v>
+        <v>2489</v>
       </c>
       <c r="G111">
         <v>17837</v>
@@ -4412,10 +4412,10 @@
         <v>36362</v>
       </c>
       <c r="I111">
-        <v>210319</v>
+        <v>211725</v>
       </c>
       <c r="J111">
-        <v>207050</v>
+        <v>209055</v>
       </c>
       <c r="K111" t="s">
         <v>47</v>
@@ -4429,16 +4429,16 @@
         <v>32</v>
       </c>
       <c r="C112">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D112">
-        <v>19246</v>
+        <v>20987</v>
       </c>
       <c r="E112">
-        <v>19344</v>
+        <v>19379</v>
       </c>
       <c r="F112">
-        <v>2038</v>
+        <v>2417</v>
       </c>
       <c r="G112">
         <v>16137</v>
@@ -4447,10 +4447,10 @@
         <v>23828</v>
       </c>
       <c r="I112">
-        <v>297539</v>
+        <v>295622</v>
       </c>
       <c r="J112">
-        <v>297510</v>
+        <v>293129</v>
       </c>
       <c r="K112" t="s">
         <v>47</v>
@@ -4464,16 +4464,16 @@
         <v>32</v>
       </c>
       <c r="C113">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D113">
-        <v>11996</v>
+        <v>11271</v>
       </c>
       <c r="E113">
-        <v>11278</v>
+        <v>10895</v>
       </c>
       <c r="F113">
-        <v>2371</v>
+        <v>1298</v>
       </c>
       <c r="G113">
         <v>9125</v>
@@ -4482,10 +4482,10 @@
         <v>19478</v>
       </c>
       <c r="I113">
-        <v>147681</v>
+        <v>147880</v>
       </c>
       <c r="J113">
-        <v>145087</v>
+        <v>142188</v>
       </c>
       <c r="K113" t="s">
         <v>47</v>
@@ -4499,16 +4499,16 @@
         <v>32</v>
       </c>
       <c r="C114">
-        <v>78</v>
+        <v>678</v>
       </c>
       <c r="D114">
-        <v>13030</v>
+        <v>12757</v>
       </c>
       <c r="E114">
-        <v>12972</v>
+        <v>12816</v>
       </c>
       <c r="F114">
-        <v>1160</v>
+        <v>1218</v>
       </c>
       <c r="G114">
         <v>10662</v>
@@ -4517,10 +4517,10 @@
         <v>16389</v>
       </c>
       <c r="I114">
-        <v>188723</v>
+        <v>187056</v>
       </c>
       <c r="J114">
-        <v>185156</v>
+        <v>183378</v>
       </c>
       <c r="K114" t="s">
         <v>47</v>
@@ -4534,16 +4534,16 @@
         <v>32</v>
       </c>
       <c r="C115">
-        <v>608</v>
+        <v>6032</v>
       </c>
       <c r="D115">
-        <v>18895</v>
+        <v>18945</v>
       </c>
       <c r="E115">
-        <v>18610</v>
+        <v>18815</v>
       </c>
       <c r="F115">
-        <v>2581</v>
+        <v>2188</v>
       </c>
       <c r="G115">
         <v>11595</v>
@@ -4552,10 +4552,10 @@
         <v>37715</v>
       </c>
       <c r="I115">
-        <v>287813</v>
+        <v>288197</v>
       </c>
       <c r="J115">
-        <v>284915</v>
+        <v>286437</v>
       </c>
       <c r="K115" t="s">
         <v>47</v>
@@ -4569,16 +4569,16 @@
         <v>32</v>
       </c>
       <c r="C116">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D116">
-        <v>14806</v>
+        <v>15257</v>
       </c>
       <c r="E116">
-        <v>14544</v>
+        <v>15104</v>
       </c>
       <c r="F116">
-        <v>2151</v>
+        <v>2285</v>
       </c>
       <c r="G116">
         <v>10489</v>
@@ -4587,10 +4587,10 @@
         <v>24901</v>
       </c>
       <c r="I116">
-        <v>206808</v>
+        <v>206325</v>
       </c>
       <c r="J116">
-        <v>202306</v>
+        <v>202514</v>
       </c>
       <c r="K116" t="s">
         <v>47</v>
@@ -4604,16 +4604,16 @@
         <v>32</v>
       </c>
       <c r="C117">
-        <v>337</v>
+        <v>3049</v>
       </c>
       <c r="D117">
-        <v>19395</v>
+        <v>18932</v>
       </c>
       <c r="E117">
-        <v>18618</v>
+        <v>18065</v>
       </c>
       <c r="F117">
-        <v>3143</v>
+        <v>2994</v>
       </c>
       <c r="G117">
         <v>13597</v>
@@ -4622,10 +4622,10 @@
         <v>29137</v>
       </c>
       <c r="I117">
-        <v>267532</v>
+        <v>269599</v>
       </c>
       <c r="J117">
-        <v>262850</v>
+        <v>264839</v>
       </c>
       <c r="K117" t="s">
         <v>47</v>
@@ -4639,16 +4639,16 @@
         <v>32</v>
       </c>
       <c r="C118">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D118">
-        <v>12949</v>
+        <v>13072</v>
       </c>
       <c r="E118">
         <v>12862</v>
       </c>
       <c r="F118">
-        <v>1657</v>
+        <v>1752</v>
       </c>
       <c r="G118">
         <v>9662</v>
@@ -4657,10 +4657,10 @@
         <v>17151</v>
       </c>
       <c r="I118">
-        <v>170443</v>
+        <v>167401</v>
       </c>
       <c r="J118">
-        <v>168589</v>
+        <v>165425</v>
       </c>
       <c r="K118" t="s">
         <v>47</v>
@@ -4674,16 +4674,16 @@
         <v>32</v>
       </c>
       <c r="C119">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D119">
-        <v>9871</v>
+        <v>9306</v>
       </c>
       <c r="E119">
-        <v>9770</v>
+        <v>9247</v>
       </c>
       <c r="F119">
-        <v>786</v>
+        <v>285</v>
       </c>
       <c r="G119">
         <v>9247</v>
@@ -4692,10 +4692,10 @@
         <v>11168</v>
       </c>
       <c r="I119">
-        <v>131958</v>
+        <v>128871</v>
       </c>
       <c r="J119">
-        <v>131877</v>
+        <v>128720</v>
       </c>
       <c r="K119" t="s">
         <v>47</v>
@@ -4709,16 +4709,16 @@
         <v>32</v>
       </c>
       <c r="C120">
-        <v>213</v>
+        <v>1653</v>
       </c>
       <c r="D120">
-        <v>16849</v>
+        <v>17397</v>
       </c>
       <c r="E120">
-        <v>16313</v>
+        <v>16990</v>
       </c>
       <c r="F120">
-        <v>2488</v>
+        <v>2725</v>
       </c>
       <c r="G120">
         <v>12834</v>
@@ -4727,10 +4727,10 @@
         <v>31357</v>
       </c>
       <c r="I120">
-        <v>227168</v>
+        <v>229122</v>
       </c>
       <c r="J120">
-        <v>223363</v>
+        <v>226045</v>
       </c>
       <c r="K120" t="s">
         <v>47</v>
@@ -4744,16 +4744,16 @@
         <v>32</v>
       </c>
       <c r="C121">
-        <v>494</v>
+        <v>3806</v>
       </c>
       <c r="D121">
-        <v>19812</v>
+        <v>19941</v>
       </c>
       <c r="E121">
-        <v>19322</v>
+        <v>19440</v>
       </c>
       <c r="F121">
-        <v>3392</v>
+        <v>3579</v>
       </c>
       <c r="G121">
         <v>12743</v>
@@ -4762,10 +4762,10 @@
         <v>34929</v>
       </c>
       <c r="I121">
-        <v>249288</v>
+        <v>250609</v>
       </c>
       <c r="J121">
-        <v>244876</v>
+        <v>245405</v>
       </c>
       <c r="K121" t="s">
         <v>47</v>
@@ -4779,16 +4779,16 @@
         <v>32</v>
       </c>
       <c r="C122">
-        <v>329</v>
+        <v>2801</v>
       </c>
       <c r="D122">
-        <v>19729</v>
+        <v>20146</v>
       </c>
       <c r="E122">
-        <v>19800</v>
+        <v>19940</v>
       </c>
       <c r="F122">
-        <v>4258</v>
+        <v>4316</v>
       </c>
       <c r="G122">
         <v>4707</v>
@@ -4797,10 +4797,10 @@
         <v>35029</v>
       </c>
       <c r="I122">
-        <v>288454</v>
+        <v>292186</v>
       </c>
       <c r="J122">
-        <v>289416</v>
+        <v>293247</v>
       </c>
       <c r="K122" t="s">
         <v>47</v>
@@ -4814,16 +4814,16 @@
         <v>33</v>
       </c>
       <c r="C123">
-        <v>333</v>
+        <v>2997</v>
       </c>
       <c r="D123">
-        <v>12237</v>
+        <v>12443</v>
       </c>
       <c r="E123">
-        <v>11785</v>
+        <v>12057</v>
       </c>
       <c r="F123">
-        <v>5396</v>
+        <v>5634</v>
       </c>
       <c r="G123">
         <v>1138</v>
@@ -4832,10 +4832,10 @@
         <v>49042</v>
       </c>
       <c r="I123">
-        <v>279769</v>
+        <v>282042</v>
       </c>
       <c r="J123">
-        <v>274635</v>
+        <v>276896</v>
       </c>
       <c r="K123" t="s">
         <v>48</v>
@@ -4849,16 +4849,16 @@
         <v>33</v>
       </c>
       <c r="C124">
-        <v>275</v>
+        <v>2123</v>
       </c>
       <c r="D124">
-        <v>11010</v>
+        <v>11919</v>
       </c>
       <c r="E124">
-        <v>10205</v>
+        <v>10964</v>
       </c>
       <c r="F124">
-        <v>6273</v>
+        <v>6339</v>
       </c>
       <c r="G124">
         <v>22</v>
@@ -4867,10 +4867,10 @@
         <v>46883</v>
       </c>
       <c r="I124">
-        <v>299464</v>
+        <v>304105</v>
       </c>
       <c r="J124">
-        <v>299621</v>
+        <v>304211</v>
       </c>
       <c r="K124" t="s">
         <v>48</v>
@@ -4884,16 +4884,16 @@
         <v>33</v>
       </c>
       <c r="C125">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D125">
-        <v>13781</v>
+        <v>10760</v>
       </c>
       <c r="E125">
-        <v>13539</v>
+        <v>13340</v>
       </c>
       <c r="F125">
-        <v>4457</v>
+        <v>4270</v>
       </c>
       <c r="G125">
         <v>6041</v>
@@ -4902,10 +4902,10 @@
         <v>23461</v>
       </c>
       <c r="I125">
-        <v>311320</v>
+        <v>306382</v>
       </c>
       <c r="J125">
-        <v>311049</v>
+        <v>306469</v>
       </c>
       <c r="K125" t="s">
         <v>48</v>
@@ -4919,16 +4919,16 @@
         <v>33</v>
       </c>
       <c r="C126">
-        <v>491</v>
+        <v>3779</v>
       </c>
       <c r="D126">
-        <v>11714</v>
+        <v>11611</v>
       </c>
       <c r="E126">
-        <v>11525</v>
+        <v>11415</v>
       </c>
       <c r="F126">
-        <v>4621</v>
+        <v>4553</v>
       </c>
       <c r="G126">
         <v>78</v>
@@ -4937,10 +4937,10 @@
         <v>27723</v>
       </c>
       <c r="I126">
-        <v>261002</v>
+        <v>262220</v>
       </c>
       <c r="J126">
-        <v>256401</v>
+        <v>256820</v>
       </c>
       <c r="K126" t="s">
         <v>48</v>
@@ -4954,16 +4954,16 @@
         <v>33</v>
       </c>
       <c r="C127">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D127">
-        <v>8997</v>
+        <v>8513</v>
       </c>
       <c r="E127">
-        <v>8728</v>
+        <v>7944</v>
       </c>
       <c r="F127">
-        <v>4829</v>
+        <v>5076</v>
       </c>
       <c r="G127">
         <v>85</v>
@@ -4972,10 +4972,10 @@
         <v>32348</v>
       </c>
       <c r="I127">
-        <v>215805</v>
+        <v>214838</v>
       </c>
       <c r="J127">
-        <v>211034</v>
+        <v>210458</v>
       </c>
       <c r="K127" t="s">
         <v>48</v>
@@ -4989,16 +4989,16 @@
         <v>33</v>
       </c>
       <c r="C128">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="D128">
-        <v>2786</v>
+        <v>2704</v>
       </c>
       <c r="E128">
-        <v>2248</v>
+        <v>2158</v>
       </c>
       <c r="F128">
-        <v>1919</v>
+        <v>1810</v>
       </c>
       <c r="G128">
         <v>20</v>
@@ -5007,10 +5007,10 @@
         <v>9331</v>
       </c>
       <c r="I128">
-        <v>173229</v>
+        <v>170105</v>
       </c>
       <c r="J128">
-        <v>170837</v>
+        <v>167583</v>
       </c>
       <c r="K128" t="s">
         <v>48</v>
@@ -5024,16 +5024,16 @@
         <v>33</v>
       </c>
       <c r="C129">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D129">
-        <v>2515</v>
+        <v>976</v>
       </c>
       <c r="E129">
-        <v>1277</v>
+        <v>740</v>
       </c>
       <c r="F129">
-        <v>4379</v>
+        <v>1522</v>
       </c>
       <c r="G129">
         <v>13</v>
@@ -5042,10 +5042,10 @@
         <v>19272</v>
       </c>
       <c r="I129">
-        <v>150196</v>
+        <v>148856</v>
       </c>
       <c r="J129">
-        <v>146364</v>
+        <v>142928</v>
       </c>
       <c r="K129" t="s">
         <v>48</v>
@@ -5059,16 +5059,16 @@
         <v>33</v>
       </c>
       <c r="C130">
-        <v>78</v>
+        <v>678</v>
       </c>
       <c r="D130">
-        <v>5608</v>
+        <v>6963</v>
       </c>
       <c r="E130">
-        <v>4719</v>
+        <v>4496</v>
       </c>
       <c r="F130">
-        <v>5550</v>
+        <v>8148</v>
       </c>
       <c r="G130">
         <v>10</v>
@@ -5077,10 +5077,10 @@
         <v>44096</v>
       </c>
       <c r="I130">
-        <v>194331</v>
+        <v>194019</v>
       </c>
       <c r="J130">
-        <v>189875</v>
+        <v>187874</v>
       </c>
       <c r="K130" t="s">
         <v>48</v>
@@ -5094,16 +5094,16 @@
         <v>33</v>
       </c>
       <c r="C131">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D131">
-        <v>1716</v>
+        <v>868</v>
       </c>
       <c r="E131">
         <v>775</v>
       </c>
       <c r="F131">
-        <v>2833</v>
+        <v>833</v>
       </c>
       <c r="G131">
         <v>16</v>
@@ -5112,10 +5112,10 @@
         <v>6748</v>
       </c>
       <c r="I131">
-        <v>133674</v>
+        <v>129739</v>
       </c>
       <c r="J131">
-        <v>132652</v>
+        <v>129495</v>
       </c>
       <c r="K131" t="s">
         <v>48</v>
@@ -5129,16 +5129,16 @@
         <v>33</v>
       </c>
       <c r="C132">
-        <v>212</v>
+        <v>1652</v>
       </c>
       <c r="D132">
-        <v>12125</v>
+        <v>12130</v>
       </c>
       <c r="E132">
-        <v>11956</v>
+        <v>12316</v>
       </c>
       <c r="F132">
-        <v>4632</v>
+        <v>5108</v>
       </c>
       <c r="G132">
         <v>178</v>
@@ -5147,10 +5147,10 @@
         <v>24223</v>
       </c>
       <c r="I132">
-        <v>239293</v>
+        <v>241252</v>
       </c>
       <c r="J132">
-        <v>235319</v>
+        <v>238361</v>
       </c>
       <c r="K132" t="s">
         <v>48</v>
@@ -5164,16 +5164,16 @@
         <v>33</v>
       </c>
       <c r="C133">
-        <v>606</v>
+        <v>6030</v>
       </c>
       <c r="D133">
-        <v>12824</v>
+        <v>13033</v>
       </c>
       <c r="E133">
-        <v>12708</v>
+        <v>12702</v>
       </c>
       <c r="F133">
-        <v>4499</v>
+        <v>4751</v>
       </c>
       <c r="G133">
         <v>1158</v>
@@ -5182,10 +5182,10 @@
         <v>31723</v>
       </c>
       <c r="I133">
-        <v>300637</v>
+        <v>301230</v>
       </c>
       <c r="J133">
-        <v>297623</v>
+        <v>299139</v>
       </c>
       <c r="K133" t="s">
         <v>48</v>
@@ -5199,16 +5199,16 @@
         <v>34</v>
       </c>
       <c r="C134">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D134">
-        <v>14100</v>
+        <v>14185</v>
       </c>
       <c r="E134">
-        <v>14450</v>
+        <v>14755</v>
       </c>
       <c r="F134">
-        <v>1279</v>
+        <v>1188</v>
       </c>
       <c r="G134">
         <v>11992</v>
@@ -5217,10 +5217,10 @@
         <v>16180</v>
       </c>
       <c r="I134">
-        <v>164296</v>
+        <v>163041</v>
       </c>
       <c r="J134">
-        <v>160814</v>
+        <v>157683</v>
       </c>
       <c r="K134" t="s">
         <v>49</v>
@@ -5234,16 +5234,16 @@
         <v>34</v>
       </c>
       <c r="C135">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D135">
-        <v>15022</v>
+        <v>14941</v>
       </c>
       <c r="E135">
-        <v>14876</v>
+        <v>14872</v>
       </c>
       <c r="F135">
-        <v>1322</v>
+        <v>1271</v>
       </c>
       <c r="G135">
         <v>12655</v>
@@ -5252,10 +5252,10 @@
         <v>18417</v>
       </c>
       <c r="I135">
-        <v>188251</v>
+        <v>185046</v>
       </c>
       <c r="J135">
-        <v>185713</v>
+        <v>182455</v>
       </c>
       <c r="K135" t="s">
         <v>49</v>
@@ -5269,16 +5269,16 @@
         <v>34</v>
       </c>
       <c r="C136">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D136">
-        <v>14317</v>
+        <v>14358</v>
       </c>
       <c r="E136">
         <v>14622</v>
       </c>
       <c r="F136">
-        <v>602</v>
+        <v>358</v>
       </c>
       <c r="G136">
         <v>13392</v>
@@ -5287,10 +5287,10 @@
         <v>14846</v>
       </c>
       <c r="I136">
-        <v>147991</v>
+        <v>144097</v>
       </c>
       <c r="J136">
-        <v>147274</v>
+        <v>144117</v>
       </c>
       <c r="K136" t="s">
         <v>49</v>
@@ -5304,16 +5304,16 @@
         <v>34</v>
       </c>
       <c r="C137">
-        <v>203</v>
+        <v>1691</v>
       </c>
       <c r="D137">
-        <v>24876</v>
+        <v>25052</v>
       </c>
       <c r="E137">
-        <v>24499</v>
+        <v>24470</v>
       </c>
       <c r="F137">
-        <v>5187</v>
+        <v>5075</v>
       </c>
       <c r="G137">
         <v>14438</v>
@@ -5322,10 +5322,10 @@
         <v>40403</v>
       </c>
       <c r="I137">
-        <v>324340</v>
+        <v>329157</v>
       </c>
       <c r="J137">
-        <v>324120</v>
+        <v>328681</v>
       </c>
       <c r="K137" t="s">
         <v>49</v>
@@ -5339,16 +5339,16 @@
         <v>34</v>
       </c>
       <c r="C138">
-        <v>211</v>
+        <v>1651</v>
       </c>
       <c r="D138">
-        <v>19189</v>
+        <v>19378</v>
       </c>
       <c r="E138">
-        <v>18484</v>
+        <v>18476</v>
       </c>
       <c r="F138">
-        <v>3820</v>
+        <v>5760</v>
       </c>
       <c r="G138">
         <v>14959</v>
@@ -5357,10 +5357,10 @@
         <v>61869</v>
       </c>
       <c r="I138">
-        <v>258482</v>
+        <v>260630</v>
       </c>
       <c r="J138">
-        <v>253803</v>
+        <v>256837</v>
       </c>
       <c r="K138" t="s">
         <v>49</v>
@@ -5374,16 +5374,16 @@
         <v>34</v>
       </c>
       <c r="C139">
-        <v>490</v>
+        <v>3754</v>
       </c>
       <c r="D139">
-        <v>19086</v>
+        <v>18792</v>
       </c>
       <c r="E139">
-        <v>18846</v>
+        <v>18507</v>
       </c>
       <c r="F139">
-        <v>2077</v>
+        <v>1909</v>
       </c>
       <c r="G139">
         <v>14518</v>
@@ -5392,10 +5392,10 @@
         <v>29967</v>
       </c>
       <c r="I139">
-        <v>280088</v>
+        <v>281012</v>
       </c>
       <c r="J139">
-        <v>275247</v>
+        <v>275327</v>
       </c>
       <c r="K139" t="s">
         <v>49</v>
@@ -5409,16 +5409,16 @@
         <v>34</v>
       </c>
       <c r="C140">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D140">
-        <v>25137</v>
+        <v>26747</v>
       </c>
       <c r="E140">
-        <v>24756</v>
+        <v>24912</v>
       </c>
       <c r="F140">
-        <v>3002</v>
+        <v>2743</v>
       </c>
       <c r="G140">
         <v>20476</v>
@@ -5427,10 +5427,10 @@
         <v>31909</v>
       </c>
       <c r="I140">
-        <v>336457</v>
+        <v>333129</v>
       </c>
       <c r="J140">
-        <v>335805</v>
+        <v>331381</v>
       </c>
       <c r="K140" t="s">
         <v>49</v>
@@ -5444,16 +5444,16 @@
         <v>34</v>
       </c>
       <c r="C141">
-        <v>607</v>
+        <v>6031</v>
       </c>
       <c r="D141">
-        <v>23866</v>
+        <v>23694</v>
       </c>
       <c r="E141">
-        <v>23125</v>
+        <v>22954</v>
       </c>
       <c r="F141">
-        <v>3871</v>
+        <v>4014</v>
       </c>
       <c r="G141">
         <v>16638</v>
@@ -5462,10 +5462,10 @@
         <v>58339</v>
       </c>
       <c r="I141">
-        <v>324503</v>
+        <v>324924</v>
       </c>
       <c r="J141">
-        <v>320748</v>
+        <v>322093</v>
       </c>
       <c r="K141" t="s">
         <v>49</v>
@@ -5479,16 +5479,16 @@
         <v>34</v>
       </c>
       <c r="C142">
-        <v>335</v>
+        <v>3023</v>
       </c>
       <c r="D142">
-        <v>20719</v>
+        <v>20658</v>
       </c>
       <c r="E142">
-        <v>20311</v>
+        <v>20038</v>
       </c>
       <c r="F142">
-        <v>2806</v>
+        <v>3394</v>
       </c>
       <c r="G142">
         <v>16260</v>
@@ -5497,10 +5497,10 @@
         <v>48760</v>
       </c>
       <c r="I142">
-        <v>300488</v>
+        <v>302700</v>
       </c>
       <c r="J142">
-        <v>294946</v>
+        <v>296934</v>
       </c>
       <c r="K142" t="s">
         <v>49</v>
@@ -5514,16 +5514,16 @@
         <v>34</v>
       </c>
       <c r="C143">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D143">
-        <v>18111</v>
+        <v>17873</v>
       </c>
       <c r="E143">
-        <v>17746</v>
+        <v>17781</v>
       </c>
       <c r="F143">
-        <v>2316</v>
+        <v>2116</v>
       </c>
       <c r="G143">
         <v>13370</v>
@@ -5532,10 +5532,10 @@
         <v>33155</v>
       </c>
       <c r="I143">
-        <v>233916</v>
+        <v>232711</v>
       </c>
       <c r="J143">
-        <v>228780</v>
+        <v>228239</v>
       </c>
       <c r="K143" t="s">
         <v>49</v>
@@ -5549,16 +5549,16 @@
         <v>34</v>
       </c>
       <c r="C144">
-        <v>80</v>
+        <v>680</v>
       </c>
       <c r="D144">
-        <v>16524</v>
+        <v>16003</v>
       </c>
       <c r="E144">
-        <v>16722</v>
+        <v>15649</v>
       </c>
       <c r="F144">
-        <v>1822</v>
+        <v>1967</v>
       </c>
       <c r="G144">
         <v>12916</v>
@@ -5567,10 +5567,10 @@
         <v>22927</v>
       </c>
       <c r="I144">
-        <v>210855</v>
+        <v>210022</v>
       </c>
       <c r="J144">
-        <v>206597</v>
+        <v>203523</v>
       </c>
       <c r="K144" t="s">
         <v>49</v>
@@ -5584,16 +5584,16 @@
         <v>35</v>
       </c>
       <c r="C145">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D145">
-        <v>14012</v>
+        <v>14358</v>
       </c>
       <c r="E145">
-        <v>14020</v>
+        <v>14070</v>
       </c>
       <c r="F145">
-        <v>446</v>
+        <v>353</v>
       </c>
       <c r="G145">
         <v>13623</v>
@@ -5602,10 +5602,10 @@
         <v>14717</v>
       </c>
       <c r="I145">
-        <v>162003</v>
+        <v>158455</v>
       </c>
       <c r="J145">
-        <v>161294</v>
+        <v>158187</v>
       </c>
       <c r="K145" t="s">
         <v>49</v>
@@ -5619,16 +5619,16 @@
         <v>35</v>
       </c>
       <c r="C146">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D146">
-        <v>15353</v>
+        <v>15440</v>
       </c>
       <c r="E146">
-        <v>15206</v>
+        <v>15758</v>
       </c>
       <c r="F146">
-        <v>1270</v>
+        <v>947</v>
       </c>
       <c r="G146">
         <v>13037</v>
@@ -5637,10 +5637,10 @@
         <v>19398</v>
       </c>
       <c r="I146">
-        <v>203604</v>
+        <v>200486</v>
       </c>
       <c r="J146">
-        <v>200919</v>
+        <v>198213</v>
       </c>
       <c r="K146" t="s">
         <v>49</v>
@@ -5654,16 +5654,16 @@
         <v>35</v>
       </c>
       <c r="C147">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D147">
-        <v>21159</v>
+        <v>20811</v>
       </c>
       <c r="E147">
-        <v>20941</v>
+        <v>21448</v>
       </c>
       <c r="F147">
-        <v>4173</v>
+        <v>3368</v>
       </c>
       <c r="G147">
         <v>13871</v>
@@ -5672,10 +5672,10 @@
         <v>49692</v>
       </c>
       <c r="I147">
-        <v>255075</v>
+        <v>253522</v>
       </c>
       <c r="J147">
-        <v>249721</v>
+        <v>249687</v>
       </c>
       <c r="K147" t="s">
         <v>49</v>
@@ -5689,16 +5689,16 @@
         <v>35</v>
       </c>
       <c r="C148">
-        <v>610</v>
+        <v>6034</v>
       </c>
       <c r="D148">
-        <v>26975</v>
+        <v>26419</v>
       </c>
       <c r="E148">
-        <v>26484</v>
+        <v>26223</v>
       </c>
       <c r="F148">
-        <v>3819</v>
+        <v>3696</v>
       </c>
       <c r="G148">
         <v>17569</v>
@@ -5707,10 +5707,10 @@
         <v>47385</v>
       </c>
       <c r="I148">
-        <v>351478</v>
+        <v>351343</v>
       </c>
       <c r="J148">
-        <v>347232</v>
+        <v>348316</v>
       </c>
       <c r="K148" t="s">
         <v>49</v>
@@ -5724,16 +5724,16 @@
         <v>35</v>
       </c>
       <c r="C149">
-        <v>213</v>
+        <v>1677</v>
       </c>
       <c r="D149">
-        <v>20384</v>
+        <v>19737</v>
       </c>
       <c r="E149">
-        <v>19684</v>
+        <v>19349</v>
       </c>
       <c r="F149">
-        <v>3139</v>
+        <v>2881</v>
       </c>
       <c r="G149">
         <v>15966</v>
@@ -5742,10 +5742,10 @@
         <v>37714</v>
       </c>
       <c r="I149">
-        <v>278866</v>
+        <v>280367</v>
       </c>
       <c r="J149">
-        <v>273487</v>
+        <v>276186</v>
       </c>
       <c r="K149" t="s">
         <v>49</v>
@@ -5759,16 +5759,16 @@
         <v>35</v>
       </c>
       <c r="C150">
-        <v>492</v>
+        <v>3780</v>
       </c>
       <c r="D150">
-        <v>22775</v>
+        <v>23193</v>
       </c>
       <c r="E150">
-        <v>22140</v>
+        <v>22501</v>
       </c>
       <c r="F150">
-        <v>3902</v>
+        <v>3838</v>
       </c>
       <c r="G150">
         <v>15714</v>
@@ -5777,10 +5777,10 @@
         <v>61974</v>
       </c>
       <c r="I150">
-        <v>302863</v>
+        <v>304205</v>
       </c>
       <c r="J150">
-        <v>297387</v>
+        <v>297828</v>
       </c>
       <c r="K150" t="s">
         <v>49</v>
@@ -5794,16 +5794,16 @@
         <v>35</v>
       </c>
       <c r="C151">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D151">
-        <v>13936</v>
+        <v>13983</v>
       </c>
       <c r="E151">
-        <v>13824</v>
+        <v>13322</v>
       </c>
       <c r="F151">
-        <v>1251</v>
+        <v>986</v>
       </c>
       <c r="G151">
         <v>11666</v>
@@ -5812,10 +5812,10 @@
         <v>15670</v>
       </c>
       <c r="I151">
-        <v>178232</v>
+        <v>177024</v>
       </c>
       <c r="J151">
-        <v>174638</v>
+        <v>171005</v>
       </c>
       <c r="K151" t="s">
         <v>49</v>
@@ -5829,16 +5829,16 @@
         <v>35</v>
       </c>
       <c r="C152">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D152">
-        <v>28245</v>
+        <v>29983</v>
       </c>
       <c r="E152">
         <v>28863</v>
       </c>
       <c r="F152">
-        <v>3971</v>
+        <v>3963</v>
       </c>
       <c r="G152">
         <v>21963</v>
@@ -5847,10 +5847,10 @@
         <v>35657</v>
       </c>
       <c r="I152">
-        <v>364702</v>
+        <v>363112</v>
       </c>
       <c r="J152">
-        <v>364668</v>
+        <v>360244</v>
       </c>
       <c r="K152" t="s">
         <v>49</v>
@@ -5864,16 +5864,16 @@
         <v>35</v>
       </c>
       <c r="C153">
-        <v>170</v>
+        <v>1418</v>
       </c>
       <c r="D153">
-        <v>26414</v>
+        <v>26656</v>
       </c>
       <c r="E153">
         <v>26408</v>
       </c>
       <c r="F153">
-        <v>4648</v>
+        <v>5267</v>
       </c>
       <c r="G153">
         <v>15309</v>
@@ -5882,10 +5882,10 @@
         <v>42770</v>
       </c>
       <c r="I153">
-        <v>350754</v>
+        <v>355813</v>
       </c>
       <c r="J153">
-        <v>350528</v>
+        <v>355089</v>
       </c>
       <c r="K153" t="s">
         <v>49</v>
@@ -5899,16 +5899,16 @@
         <v>35</v>
       </c>
       <c r="C154">
-        <v>338</v>
+        <v>3050</v>
       </c>
       <c r="D154">
-        <v>26973</v>
+        <v>27410</v>
       </c>
       <c r="E154">
-        <v>26514</v>
+        <v>26961</v>
       </c>
       <c r="F154">
-        <v>4805</v>
+        <v>5757</v>
       </c>
       <c r="G154">
         <v>16078</v>
@@ -5917,10 +5917,10 @@
         <v>55882</v>
       </c>
       <c r="I154">
-        <v>327461</v>
+        <v>330110</v>
       </c>
       <c r="J154">
-        <v>321460</v>
+        <v>323895</v>
       </c>
       <c r="K154" t="s">
         <v>49</v>
@@ -5934,16 +5934,16 @@
         <v>35</v>
       </c>
       <c r="C155">
-        <v>80</v>
+        <v>680</v>
       </c>
       <c r="D155">
-        <v>19089</v>
+        <v>17985</v>
       </c>
       <c r="E155">
-        <v>18565</v>
+        <v>17396</v>
       </c>
       <c r="F155">
-        <v>3504</v>
+        <v>3013</v>
       </c>
       <c r="G155">
         <v>13265</v>
@@ -5952,10 +5952,10 @@
         <v>31455</v>
       </c>
       <c r="I155">
-        <v>229944</v>
+        <v>228007</v>
       </c>
       <c r="J155">
-        <v>225162</v>
+        <v>220919</v>
       </c>
       <c r="K155" t="s">
         <v>49</v>
@@ -5969,16 +5969,16 @@
         <v>36</v>
       </c>
       <c r="C156">
-        <v>79</v>
+        <v>679</v>
       </c>
       <c r="D156">
-        <v>5870</v>
+        <v>6792</v>
       </c>
       <c r="E156">
-        <v>5394</v>
+        <v>6228</v>
       </c>
       <c r="F156">
-        <v>3065</v>
+        <v>3553</v>
       </c>
       <c r="G156">
         <v>645</v>
@@ -5987,10 +5987,10 @@
         <v>13698</v>
       </c>
       <c r="I156">
-        <v>235814</v>
+        <v>234799</v>
       </c>
       <c r="J156">
-        <v>230556</v>
+        <v>227147</v>
       </c>
       <c r="K156" t="s">
         <v>50</v>
@@ -6004,16 +6004,16 @@
         <v>36</v>
       </c>
       <c r="C157">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D157">
-        <v>1052</v>
+        <v>877</v>
       </c>
       <c r="E157">
-        <v>928</v>
+        <v>758</v>
       </c>
       <c r="F157">
-        <v>848</v>
+        <v>390</v>
       </c>
       <c r="G157">
         <v>5</v>
@@ -6022,10 +6022,10 @@
         <v>3597</v>
       </c>
       <c r="I157">
-        <v>179284</v>
+        <v>177901</v>
       </c>
       <c r="J157">
-        <v>175566</v>
+        <v>171763</v>
       </c>
       <c r="K157" t="s">
         <v>50</v>
@@ -6039,16 +6039,16 @@
         <v>36</v>
       </c>
       <c r="C158">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D158">
-        <v>10684</v>
+        <v>11168</v>
       </c>
       <c r="E158">
         <v>11549</v>
       </c>
       <c r="F158">
-        <v>4616</v>
+        <v>2333</v>
       </c>
       <c r="G158">
         <v>1170</v>
@@ -6057,10 +6057,10 @@
         <v>19757</v>
       </c>
       <c r="I158">
-        <v>375386</v>
+        <v>374280</v>
       </c>
       <c r="J158">
-        <v>376217</v>
+        <v>371793</v>
       </c>
       <c r="K158" t="s">
         <v>50</v>
@@ -6074,16 +6074,16 @@
         <v>36</v>
       </c>
       <c r="C159">
-        <v>163</v>
+        <v>1339</v>
       </c>
       <c r="D159">
-        <v>10672</v>
+        <v>9978</v>
       </c>
       <c r="E159">
-        <v>10562</v>
+        <v>9850</v>
       </c>
       <c r="F159">
-        <v>5818</v>
+        <v>4866</v>
       </c>
       <c r="G159">
         <v>223</v>
@@ -6092,10 +6092,10 @@
         <v>55440</v>
       </c>
       <c r="I159">
-        <v>361426</v>
+        <v>365791</v>
       </c>
       <c r="J159">
-        <v>361090</v>
+        <v>364939</v>
       </c>
       <c r="K159" t="s">
         <v>50</v>
@@ -6109,16 +6109,16 @@
         <v>36</v>
       </c>
       <c r="C160">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D160">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E160">
         <v>963</v>
       </c>
       <c r="F160">
-        <v>213</v>
+        <v>59</v>
       </c>
       <c r="G160">
         <v>607</v>
@@ -6127,10 +6127,10 @@
         <v>1136</v>
       </c>
       <c r="I160">
-        <v>162959</v>
+        <v>159413</v>
       </c>
       <c r="J160">
-        <v>162257</v>
+        <v>159150</v>
       </c>
       <c r="K160" t="s">
         <v>50</v>
@@ -6144,16 +6144,16 @@
         <v>36</v>
       </c>
       <c r="C161">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D161">
-        <v>5611</v>
+        <v>6917</v>
       </c>
       <c r="E161">
-        <v>4634</v>
+        <v>5762</v>
       </c>
       <c r="F161">
-        <v>3621</v>
+        <v>4527</v>
       </c>
       <c r="G161">
         <v>773</v>
@@ -6162,10 +6162,10 @@
         <v>22102</v>
       </c>
       <c r="I161">
-        <v>260686</v>
+        <v>260439</v>
       </c>
       <c r="J161">
-        <v>254355</v>
+        <v>255449</v>
       </c>
       <c r="K161" t="s">
         <v>50</v>
@@ -6179,16 +6179,16 @@
         <v>36</v>
       </c>
       <c r="C162">
-        <v>333</v>
+        <v>2997</v>
       </c>
       <c r="D162">
-        <v>11165</v>
+        <v>10044</v>
       </c>
       <c r="E162">
-        <v>10773</v>
+        <v>10160</v>
       </c>
       <c r="F162">
-        <v>5488</v>
+        <v>5449</v>
       </c>
       <c r="G162">
         <v>1451</v>
@@ -6197,10 +6197,10 @@
         <v>35520</v>
       </c>
       <c r="I162">
-        <v>338626</v>
+        <v>340154</v>
       </c>
       <c r="J162">
-        <v>332233</v>
+        <v>334055</v>
       </c>
       <c r="K162" t="s">
         <v>50</v>
@@ -6214,16 +6214,16 @@
         <v>36</v>
       </c>
       <c r="C163">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D163">
-        <v>3304</v>
+        <v>3205</v>
       </c>
       <c r="E163">
-        <v>2714</v>
+        <v>2884</v>
       </c>
       <c r="F163">
-        <v>2501</v>
+        <v>2162</v>
       </c>
       <c r="G163">
         <v>614</v>
@@ -6232,10 +6232,10 @@
         <v>10276</v>
       </c>
       <c r="I163">
-        <v>206908</v>
+        <v>203691</v>
       </c>
       <c r="J163">
-        <v>203633</v>
+        <v>201097</v>
       </c>
       <c r="K163" t="s">
         <v>50</v>
@@ -6249,16 +6249,16 @@
         <v>36</v>
       </c>
       <c r="C164">
-        <v>491</v>
+        <v>3803</v>
       </c>
       <c r="D164">
-        <v>12339</v>
+        <v>11474</v>
       </c>
       <c r="E164">
-        <v>12140</v>
+        <v>11569</v>
       </c>
       <c r="F164">
-        <v>6539</v>
+        <v>5739</v>
       </c>
       <c r="G164">
         <v>1329</v>
@@ -6267,10 +6267,10 @@
         <v>43770</v>
       </c>
       <c r="I164">
-        <v>315202</v>
+        <v>315679</v>
       </c>
       <c r="J164">
-        <v>309527</v>
+        <v>309397</v>
       </c>
       <c r="K164" t="s">
         <v>50</v>
@@ -6284,16 +6284,16 @@
         <v>36</v>
       </c>
       <c r="C165">
-        <v>213</v>
+        <v>1677</v>
       </c>
       <c r="D165">
-        <v>7582</v>
+        <v>7211</v>
       </c>
       <c r="E165">
-        <v>6931</v>
+        <v>6624</v>
       </c>
       <c r="F165">
-        <v>4470</v>
+        <v>4679</v>
       </c>
       <c r="G165">
         <v>218</v>
@@ -6302,10 +6302,10 @@
         <v>30313</v>
       </c>
       <c r="I165">
-        <v>286448</v>
+        <v>287578</v>
       </c>
       <c r="J165">
-        <v>280418</v>
+        <v>282810</v>
       </c>
       <c r="K165" t="s">
         <v>50</v>
@@ -6319,16 +6319,16 @@
         <v>36</v>
       </c>
       <c r="C166">
-        <v>607</v>
+        <v>5959</v>
       </c>
       <c r="D166">
-        <v>11406</v>
+        <v>11523</v>
       </c>
       <c r="E166">
-        <v>11283</v>
+        <v>11445</v>
       </c>
       <c r="F166">
-        <v>4746</v>
+        <v>4505</v>
       </c>
       <c r="G166">
         <v>274</v>
@@ -6337,10 +6337,10 @@
         <v>27922</v>
       </c>
       <c r="I166">
-        <v>362884</v>
+        <v>362866</v>
       </c>
       <c r="J166">
-        <v>358515</v>
+        <v>359761</v>
       </c>
       <c r="K166" t="s">
         <v>50</v>
@@ -6354,16 +6354,16 @@
         <v>37</v>
       </c>
       <c r="C167">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D167">
-        <v>45060</v>
+        <v>44229</v>
       </c>
       <c r="E167">
-        <v>45542</v>
+        <v>43181</v>
       </c>
       <c r="F167">
-        <v>5710</v>
+        <v>3897</v>
       </c>
       <c r="G167">
         <v>31888</v>
@@ -6372,10 +6372,10 @@
         <v>88203</v>
       </c>
       <c r="I167">
-        <v>305746</v>
+        <v>304668</v>
       </c>
       <c r="J167">
-        <v>299897</v>
+        <v>298630</v>
       </c>
       <c r="K167" t="s">
         <v>51</v>
@@ -6389,16 +6389,16 @@
         <v>37</v>
       </c>
       <c r="C168">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D168">
-        <v>41115</v>
+        <v>41066</v>
       </c>
       <c r="E168">
-        <v>41012</v>
+        <v>38904</v>
       </c>
       <c r="F168">
-        <v>4702</v>
+        <v>5983</v>
       </c>
       <c r="G168">
         <v>31979</v>
@@ -6407,10 +6407,10 @@
         <v>54416</v>
       </c>
       <c r="I168">
-        <v>248023</v>
+        <v>244757</v>
       </c>
       <c r="J168">
-        <v>244645</v>
+        <v>240001</v>
       </c>
       <c r="K168" t="s">
         <v>51</v>
@@ -6424,16 +6424,16 @@
         <v>37</v>
       </c>
       <c r="C169">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D169">
-        <v>31124</v>
+        <v>32473</v>
       </c>
       <c r="E169">
-        <v>30434</v>
+        <v>31471</v>
       </c>
       <c r="F169">
-        <v>1598</v>
+        <v>1263</v>
       </c>
       <c r="G169">
         <v>29805</v>
@@ -6442,10 +6442,10 @@
         <v>33757</v>
       </c>
       <c r="I169">
-        <v>194083</v>
+        <v>191886</v>
       </c>
       <c r="J169">
-        <v>192691</v>
+        <v>190621</v>
       </c>
       <c r="K169" t="s">
         <v>51</v>
@@ -6459,16 +6459,16 @@
         <v>37</v>
       </c>
       <c r="C170">
-        <v>492</v>
+        <v>3804</v>
       </c>
       <c r="D170">
-        <v>49512</v>
+        <v>48581</v>
       </c>
       <c r="E170">
-        <v>48796</v>
+        <v>47785</v>
       </c>
       <c r="F170">
-        <v>6377</v>
+        <v>6274</v>
       </c>
       <c r="G170">
         <v>33689</v>
@@ -6477,10 +6477,10 @@
         <v>75231</v>
       </c>
       <c r="I170">
-        <v>364714</v>
+        <v>364260</v>
       </c>
       <c r="J170">
-        <v>358323</v>
+        <v>357182</v>
       </c>
       <c r="K170" t="s">
         <v>51</v>
@@ -6494,16 +6494,16 @@
         <v>37</v>
       </c>
       <c r="C171">
-        <v>213</v>
+        <v>1677</v>
       </c>
       <c r="D171">
-        <v>50720</v>
+        <v>49937</v>
       </c>
       <c r="E171">
-        <v>50705</v>
+        <v>49599</v>
       </c>
       <c r="F171">
-        <v>5817</v>
+        <v>5821</v>
       </c>
       <c r="G171">
         <v>33401</v>
@@ -6512,10 +6512,10 @@
         <v>69765</v>
       </c>
       <c r="I171">
-        <v>337168</v>
+        <v>337515</v>
       </c>
       <c r="J171">
-        <v>331123</v>
+        <v>332409</v>
       </c>
       <c r="K171" t="s">
         <v>51</v>
@@ -6529,16 +6529,16 @@
         <v>37</v>
       </c>
       <c r="C172">
-        <v>100</v>
+        <v>844</v>
       </c>
       <c r="D172">
-        <v>59841</v>
+        <v>61069</v>
       </c>
       <c r="E172">
-        <v>60627</v>
+        <v>62143</v>
       </c>
       <c r="F172">
-        <v>8081</v>
+        <v>7461</v>
       </c>
       <c r="G172">
         <v>38191</v>
@@ -6547,10 +6547,10 @@
         <v>79868</v>
       </c>
       <c r="I172">
-        <v>421267</v>
+        <v>426860</v>
       </c>
       <c r="J172">
-        <v>421717</v>
+        <v>427082</v>
       </c>
       <c r="K172" t="s">
         <v>51</v>
@@ -6564,16 +6564,16 @@
         <v>37</v>
       </c>
       <c r="C173">
-        <v>333</v>
+        <v>2997</v>
       </c>
       <c r="D173">
-        <v>50341</v>
+        <v>49413</v>
       </c>
       <c r="E173">
-        <v>49424</v>
+        <v>48976</v>
       </c>
       <c r="F173">
-        <v>5849</v>
+        <v>5637</v>
       </c>
       <c r="G173">
         <v>38052</v>
@@ -6582,10 +6582,10 @@
         <v>75456</v>
       </c>
       <c r="I173">
-        <v>388967</v>
+        <v>389567</v>
       </c>
       <c r="J173">
-        <v>381657</v>
+        <v>383031</v>
       </c>
       <c r="K173" t="s">
         <v>51</v>
@@ -6599,16 +6599,16 @@
         <v>37</v>
       </c>
       <c r="C174">
-        <v>80</v>
+        <v>680</v>
       </c>
       <c r="D174">
-        <v>41475</v>
+        <v>40251</v>
       </c>
       <c r="E174">
-        <v>41322</v>
+        <v>39730</v>
       </c>
       <c r="F174">
-        <v>5585</v>
+        <v>5129</v>
       </c>
       <c r="G174">
         <v>28610</v>
@@ -6617,10 +6617,10 @@
         <v>71221</v>
       </c>
       <c r="I174">
-        <v>277289</v>
+        <v>275050</v>
       </c>
       <c r="J174">
-        <v>271878</v>
+        <v>266877</v>
       </c>
       <c r="K174" t="s">
         <v>51</v>
@@ -6634,16 +6634,16 @@
         <v>37</v>
       </c>
       <c r="C175">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D175">
-        <v>60693</v>
+        <v>60245</v>
       </c>
       <c r="E175">
-        <v>60803</v>
+        <v>60634</v>
       </c>
       <c r="F175">
-        <v>4661</v>
+        <v>2393</v>
       </c>
       <c r="G175">
         <v>49354</v>
@@ -6652,10 +6652,10 @@
         <v>69237</v>
       </c>
       <c r="I175">
-        <v>436079</v>
+        <v>434525</v>
       </c>
       <c r="J175">
-        <v>437020</v>
+        <v>432427</v>
       </c>
       <c r="K175" t="s">
         <v>51</v>
@@ -6669,16 +6669,16 @@
         <v>37</v>
       </c>
       <c r="C176">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D176">
-        <v>34314</v>
+        <v>33565</v>
       </c>
       <c r="E176">
-        <v>33970</v>
+        <v>33881</v>
       </c>
       <c r="F176">
-        <v>3055</v>
+        <v>1439</v>
       </c>
       <c r="G176">
         <v>29925</v>
@@ -6687,10 +6687,10 @@
         <v>38978</v>
       </c>
       <c r="I176">
-        <v>213598</v>
+        <v>211466</v>
       </c>
       <c r="J176">
-        <v>209536</v>
+        <v>205644</v>
       </c>
       <c r="K176" t="s">
         <v>51</v>
@@ -6704,16 +6704,16 @@
         <v>37</v>
       </c>
       <c r="C177">
-        <v>606</v>
+        <v>5958</v>
       </c>
       <c r="D177">
-        <v>58529</v>
+        <v>59032</v>
       </c>
       <c r="E177">
-        <v>58354</v>
+        <v>58618</v>
       </c>
       <c r="F177">
-        <v>5743</v>
+        <v>5624</v>
       </c>
       <c r="G177">
         <v>39281</v>
@@ -6722,10 +6722,10 @@
         <v>81881</v>
       </c>
       <c r="I177">
-        <v>421413</v>
+        <v>421898</v>
       </c>
       <c r="J177">
-        <v>416869</v>
+        <v>418379</v>
       </c>
       <c r="K177" t="s">
         <v>51</v>
@@ -6739,16 +6739,16 @@
         <v>38</v>
       </c>
       <c r="C178">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="D178">
-        <v>21012</v>
+        <v>18899</v>
       </c>
       <c r="E178">
-        <v>19940</v>
+        <v>19316</v>
       </c>
       <c r="F178">
-        <v>3695</v>
+        <v>2457</v>
       </c>
       <c r="G178">
         <v>16985</v>
@@ -6757,10 +6757,10 @@
         <v>33429</v>
       </c>
       <c r="I178">
-        <v>457091</v>
+        <v>453424</v>
       </c>
       <c r="J178">
-        <v>456960</v>
+        <v>451743</v>
       </c>
       <c r="K178" t="s">
         <v>51</v>
@@ -6774,16 +6774,16 @@
         <v>38</v>
       </c>
       <c r="C179">
-        <v>335</v>
+        <v>3023</v>
       </c>
       <c r="D179">
-        <v>22734</v>
+        <v>24997</v>
       </c>
       <c r="E179">
-        <v>22507</v>
+        <v>24276</v>
       </c>
       <c r="F179">
-        <v>5533</v>
+        <v>5490</v>
       </c>
       <c r="G179">
         <v>10979</v>
@@ -6792,10 +6792,10 @@
         <v>47523</v>
       </c>
       <c r="I179">
-        <v>411701</v>
+        <v>414564</v>
       </c>
       <c r="J179">
-        <v>404164</v>
+        <v>407307</v>
       </c>
       <c r="K179" t="s">
         <v>51</v>
@@ -6809,16 +6809,16 @@
         <v>38</v>
       </c>
       <c r="C180">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="D180">
-        <v>13673</v>
+        <v>15433</v>
       </c>
       <c r="E180">
-        <v>13658</v>
+        <v>14694</v>
       </c>
       <c r="F180">
-        <v>3751</v>
+        <v>2552</v>
       </c>
       <c r="G180">
         <v>7308</v>
@@ -6827,10 +6827,10 @@
         <v>20807</v>
       </c>
       <c r="I180">
-        <v>261696</v>
+        <v>260190</v>
       </c>
       <c r="J180">
-        <v>258303</v>
+        <v>254695</v>
       </c>
       <c r="K180" t="s">
         <v>51</v>
@@ -6844,16 +6844,16 @@
         <v>38</v>
       </c>
       <c r="C181">
-        <v>56</v>
+        <v>440</v>
       </c>
       <c r="D181">
-        <v>23208</v>
+        <v>25959</v>
       </c>
       <c r="E181">
-        <v>21936</v>
+        <v>24268</v>
       </c>
       <c r="F181">
-        <v>6173</v>
+        <v>6725</v>
       </c>
       <c r="G181">
         <v>5659</v>
@@ -6862,10 +6862,10 @@
         <v>41467</v>
       </c>
       <c r="I181">
-        <v>444475</v>
+        <v>452819</v>
       </c>
       <c r="J181">
-        <v>443653</v>
+        <v>451350</v>
       </c>
       <c r="K181" t="s">
         <v>51</v>
@@ -6879,16 +6879,16 @@
         <v>38</v>
       </c>
       <c r="C182">
-        <v>596</v>
+        <v>5948</v>
       </c>
       <c r="D182">
-        <v>21336</v>
+        <v>20734</v>
       </c>
       <c r="E182">
-        <v>20530</v>
+        <v>19750</v>
       </c>
       <c r="F182">
-        <v>4722</v>
+        <v>4852</v>
       </c>
       <c r="G182">
         <v>10805</v>
@@ -6897,10 +6897,10 @@
         <v>59271</v>
       </c>
       <c r="I182">
-        <v>442749</v>
+        <v>442632</v>
       </c>
       <c r="J182">
-        <v>437399</v>
+        <v>438129</v>
       </c>
       <c r="K182" t="s">
         <v>51</v>
@@ -6914,16 +6914,16 @@
         <v>38</v>
       </c>
       <c r="C183">
-        <v>18</v>
+        <v>186</v>
       </c>
       <c r="D183">
-        <v>12981</v>
+        <v>13749</v>
       </c>
       <c r="E183">
-        <v>13238</v>
+        <v>14553</v>
       </c>
       <c r="F183">
-        <v>3255</v>
+        <v>1961</v>
       </c>
       <c r="G183">
         <v>7945</v>
@@ -6932,10 +6932,10 @@
         <v>20199</v>
       </c>
       <c r="I183">
-        <v>226579</v>
+        <v>225215</v>
       </c>
       <c r="J183">
-        <v>222774</v>
+        <v>220197</v>
       </c>
       <c r="K183" t="s">
         <v>51</v>
@@ -6949,16 +6949,16 @@
         <v>38</v>
       </c>
       <c r="C184">
-        <v>213</v>
+        <v>1653</v>
       </c>
       <c r="D184">
-        <v>16983</v>
+        <v>17347</v>
       </c>
       <c r="E184">
         <v>17077</v>
       </c>
       <c r="F184">
-        <v>4693</v>
+        <v>3116</v>
       </c>
       <c r="G184">
         <v>8086</v>
@@ -6967,10 +6967,10 @@
         <v>40417</v>
       </c>
       <c r="I184">
-        <v>354151</v>
+        <v>354862</v>
       </c>
       <c r="J184">
-        <v>348200</v>
+        <v>349486</v>
       </c>
       <c r="K184" t="s">
         <v>51</v>
@@ -6984,16 +6984,16 @@
         <v>38</v>
       </c>
       <c r="C185">
-        <v>80</v>
+        <v>680</v>
       </c>
       <c r="D185">
-        <v>14479</v>
+        <v>15293</v>
       </c>
       <c r="E185">
-        <v>14566</v>
+        <v>15011</v>
       </c>
       <c r="F185">
-        <v>3232</v>
+        <v>2673</v>
       </c>
       <c r="G185">
         <v>8030</v>
@@ -7002,10 +7002,10 @@
         <v>21810</v>
       </c>
       <c r="I185">
-        <v>291768</v>
+        <v>290343</v>
       </c>
       <c r="J185">
-        <v>286444</v>
+        <v>281888</v>
       </c>
       <c r="K185" t="s">
         <v>51</v>
@@ -7019,16 +7019,16 @@
         <v>38</v>
       </c>
       <c r="C186">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D186">
-        <v>11171</v>
+        <v>11152</v>
       </c>
       <c r="E186">
         <v>11128</v>
       </c>
       <c r="F186">
-        <v>423</v>
+        <v>221</v>
       </c>
       <c r="G186">
         <v>10650</v>
@@ -7037,10 +7037,10 @@
         <v>11775</v>
       </c>
       <c r="I186">
-        <v>205254</v>
+        <v>203038</v>
       </c>
       <c r="J186">
-        <v>203819</v>
+        <v>201749</v>
       </c>
       <c r="K186" t="s">
         <v>51</v>
@@ -7054,16 +7054,16 @@
         <v>38</v>
       </c>
       <c r="C187">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D187">
-        <v>18384</v>
+        <v>19627</v>
       </c>
       <c r="E187">
-        <v>17833</v>
+        <v>19607</v>
       </c>
       <c r="F187">
-        <v>5254</v>
+        <v>3452</v>
       </c>
       <c r="G187">
         <v>7663</v>
@@ -7072,10 +7072,10 @@
         <v>39310</v>
       </c>
       <c r="I187">
-        <v>324130</v>
+        <v>324295</v>
       </c>
       <c r="J187">
-        <v>317730</v>
+        <v>318237</v>
       </c>
       <c r="K187" t="s">
         <v>51</v>
@@ -7089,16 +7089,16 @@
         <v>38</v>
       </c>
       <c r="C188">
-        <v>488</v>
+        <v>3800</v>
       </c>
       <c r="D188">
-        <v>17444</v>
+        <v>18955</v>
       </c>
       <c r="E188">
-        <v>17972</v>
+        <v>18501</v>
       </c>
       <c r="F188">
-        <v>3897</v>
+        <v>3022</v>
       </c>
       <c r="G188">
         <v>8764</v>
@@ -7107,10 +7107,10 @@
         <v>38930</v>
       </c>
       <c r="I188">
-        <v>382158</v>
+        <v>383215</v>
       </c>
       <c r="J188">
-        <v>376295</v>
+        <v>375683</v>
       </c>
       <c r="K188" t="s">
         <v>51</v>
@@ -7124,16 +7124,16 @@
         <v>39</v>
       </c>
       <c r="C189">
-        <v>42</v>
+        <v>306</v>
       </c>
       <c r="D189">
-        <v>6830</v>
+        <v>6727</v>
       </c>
       <c r="E189">
-        <v>5799</v>
+        <v>6045</v>
       </c>
       <c r="F189">
-        <v>6718</v>
+        <v>4331</v>
       </c>
       <c r="G189">
         <v>41</v>
@@ -7142,10 +7142,10 @@
         <v>38724</v>
       </c>
       <c r="I189">
-        <v>451305</v>
+        <v>459546</v>
       </c>
       <c r="J189">
-        <v>449452</v>
+        <v>457395</v>
       </c>
       <c r="K189" t="s">
         <v>52</v>
@@ -7159,16 +7159,16 @@
         <v>39</v>
       </c>
       <c r="C190">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D190">
-        <v>810</v>
+        <v>1069</v>
       </c>
       <c r="E190">
         <v>745</v>
       </c>
       <c r="F190">
-        <v>903</v>
+        <v>1080</v>
       </c>
       <c r="G190">
         <v>7</v>
@@ -7177,10 +7177,10 @@
         <v>2186</v>
       </c>
       <c r="I190">
-        <v>206064</v>
+        <v>204107</v>
       </c>
       <c r="J190">
-        <v>204564</v>
+        <v>202494</v>
       </c>
       <c r="K190" t="s">
         <v>52</v>
@@ -7194,16 +7194,16 @@
         <v>39</v>
       </c>
       <c r="C191">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="D191">
-        <v>2265</v>
+        <v>2215</v>
       </c>
       <c r="E191">
         <v>1908</v>
       </c>
       <c r="F191">
-        <v>1539</v>
+        <v>1661</v>
       </c>
       <c r="G191">
         <v>5</v>
@@ -7212,10 +7212,10 @@
         <v>5404</v>
       </c>
       <c r="I191">
-        <v>263961</v>
+        <v>262405</v>
       </c>
       <c r="J191">
-        <v>260211</v>
+        <v>256603</v>
       </c>
       <c r="K191" t="s">
         <v>52</v>
@@ -7229,16 +7229,16 @@
         <v>39</v>
       </c>
       <c r="C192">
-        <v>321</v>
+        <v>2961</v>
       </c>
       <c r="D192">
-        <v>11431</v>
+        <v>11743</v>
       </c>
       <c r="E192">
-        <v>10427</v>
+        <v>11377</v>
       </c>
       <c r="F192">
-        <v>5877</v>
+        <v>5726</v>
       </c>
       <c r="G192">
         <v>11</v>
@@ -7247,10 +7247,10 @@
         <v>38592</v>
       </c>
       <c r="I192">
-        <v>423132</v>
+        <v>426307</v>
       </c>
       <c r="J192">
-        <v>414591</v>
+        <v>418684</v>
       </c>
       <c r="K192" t="s">
         <v>52</v>
@@ -7264,16 +7264,16 @@
         <v>39</v>
       </c>
       <c r="C193">
-        <v>78</v>
+        <v>678</v>
       </c>
       <c r="D193">
-        <v>5419</v>
+        <v>4933</v>
       </c>
       <c r="E193">
-        <v>4572</v>
+        <v>4344</v>
       </c>
       <c r="F193">
-        <v>3861</v>
+        <v>2673</v>
       </c>
       <c r="G193">
         <v>1167</v>
@@ -7282,10 +7282,10 @@
         <v>26836</v>
       </c>
       <c r="I193">
-        <v>297187</v>
+        <v>295276</v>
       </c>
       <c r="J193">
-        <v>291016</v>
+        <v>286232</v>
       </c>
       <c r="K193" t="s">
         <v>52</v>
@@ -7299,16 +7299,16 @@
         <v>39</v>
       </c>
       <c r="C194">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D194">
-        <v>8120</v>
+        <v>8407</v>
       </c>
       <c r="E194">
         <v>8154</v>
       </c>
       <c r="F194">
-        <v>1860</v>
+        <v>2921</v>
       </c>
       <c r="G194">
         <v>4710</v>
@@ -7317,10 +7317,10 @@
         <v>11678</v>
       </c>
       <c r="I194">
-        <v>465211</v>
+        <v>461831</v>
       </c>
       <c r="J194">
-        <v>465114</v>
+        <v>459897</v>
       </c>
       <c r="K194" t="s">
         <v>52</v>
@@ -7334,16 +7334,16 @@
         <v>39</v>
       </c>
       <c r="C195">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="D195">
-        <v>1990</v>
+        <v>1376</v>
       </c>
       <c r="E195">
         <v>1523</v>
       </c>
       <c r="F195">
-        <v>1950</v>
+        <v>918</v>
       </c>
       <c r="G195">
         <v>9</v>
@@ -7352,10 +7352,10 @@
         <v>8342</v>
       </c>
       <c r="I195">
-        <v>228569</v>
+        <v>226591</v>
       </c>
       <c r="J195">
-        <v>224297</v>
+        <v>221720</v>
       </c>
       <c r="K195" t="s">
         <v>52</v>
@@ -7369,16 +7369,16 @@
         <v>39</v>
       </c>
       <c r="C196">
-        <v>173</v>
+        <v>1037</v>
       </c>
       <c r="D196">
-        <v>6753</v>
+        <v>6309</v>
       </c>
       <c r="E196">
-        <v>5995</v>
+        <v>5515</v>
       </c>
       <c r="F196">
-        <v>4150</v>
+        <v>3964</v>
       </c>
       <c r="G196">
         <v>691</v>
@@ -7387,10 +7387,10 @@
         <v>20520</v>
       </c>
       <c r="I196">
-        <v>330883</v>
+        <v>330604</v>
       </c>
       <c r="J196">
-        <v>323725</v>
+        <v>323752</v>
       </c>
       <c r="K196" t="s">
         <v>52</v>
@@ -7404,16 +7404,16 @@
         <v>39</v>
       </c>
       <c r="C197">
-        <v>573</v>
+        <v>5709</v>
       </c>
       <c r="D197">
-        <v>8861</v>
+        <v>8887</v>
       </c>
       <c r="E197">
-        <v>8508</v>
+        <v>8764</v>
       </c>
       <c r="F197">
-        <v>3700</v>
+        <v>3619</v>
       </c>
       <c r="G197">
         <v>347</v>
@@ -7422,10 +7422,10 @@
         <v>28531</v>
       </c>
       <c r="I197">
-        <v>451610</v>
+        <v>451519</v>
       </c>
       <c r="J197">
-        <v>445907</v>
+        <v>446893</v>
       </c>
       <c r="K197" t="s">
         <v>52</v>
@@ -7439,16 +7439,16 @@
         <v>39</v>
       </c>
       <c r="C198">
-        <v>203</v>
+        <v>1619</v>
       </c>
       <c r="D198">
-        <v>6261</v>
+        <v>5290</v>
       </c>
       <c r="E198">
-        <v>5656</v>
+        <v>4674</v>
       </c>
       <c r="F198">
-        <v>3305</v>
+        <v>3052</v>
       </c>
       <c r="G198">
         <v>21</v>
@@ -7457,10 +7457,10 @@
         <v>18441</v>
       </c>
       <c r="I198">
-        <v>360412</v>
+        <v>360152</v>
       </c>
       <c r="J198">
-        <v>353856</v>
+        <v>354160</v>
       </c>
       <c r="K198" t="s">
         <v>52</v>
@@ -7474,16 +7474,16 @@
         <v>39</v>
       </c>
       <c r="C199">
-        <v>475</v>
+        <v>3715</v>
       </c>
       <c r="D199">
-        <v>10929</v>
+        <v>10972</v>
       </c>
       <c r="E199">
-        <v>10623</v>
+        <v>10475</v>
       </c>
       <c r="F199">
-        <v>5404</v>
+        <v>5973</v>
       </c>
       <c r="G199">
         <v>1014</v>
@@ -7492,10 +7492,10 @@
         <v>30952</v>
       </c>
       <c r="I199">
-        <v>393087</v>
+        <v>394187</v>
       </c>
       <c r="J199">
-        <v>386918</v>
+        <v>386158</v>
       </c>
       <c r="K199" t="s">
         <v>52</v>
@@ -7509,16 +7509,16 @@
         <v>40</v>
       </c>
       <c r="C200">
-        <v>326</v>
+        <v>2990</v>
       </c>
       <c r="D200">
-        <v>60934</v>
+        <v>59399</v>
       </c>
       <c r="E200">
-        <v>60129</v>
+        <v>58302</v>
       </c>
       <c r="F200">
-        <v>8401</v>
+        <v>7248</v>
       </c>
       <c r="G200">
         <v>41533</v>
@@ -7527,10 +7527,10 @@
         <v>98635</v>
       </c>
       <c r="I200">
-        <v>484066</v>
+        <v>485706</v>
       </c>
       <c r="J200">
-        <v>474720</v>
+        <v>476986</v>
       </c>
       <c r="K200" t="s">
         <v>53</v>
@@ -7544,16 +7544,16 @@
         <v>40</v>
       </c>
       <c r="C201">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="D201">
-        <v>43739</v>
+        <v>44649</v>
       </c>
       <c r="E201">
-        <v>43685</v>
+        <v>45794</v>
       </c>
       <c r="F201">
-        <v>5376</v>
+        <v>4657</v>
       </c>
       <c r="G201">
         <v>33084</v>
@@ -7562,10 +7562,10 @@
         <v>59493</v>
       </c>
       <c r="I201">
-        <v>307700</v>
+        <v>307054</v>
       </c>
       <c r="J201">
-        <v>303896</v>
+        <v>302397</v>
       </c>
       <c r="K201" t="s">
         <v>53</v>
@@ -7579,16 +7579,16 @@
         <v>40</v>
       </c>
       <c r="C202">
-        <v>585</v>
+        <v>5793</v>
       </c>
       <c r="D202">
-        <v>72783</v>
+        <v>71580</v>
       </c>
       <c r="E202">
-        <v>71867</v>
+        <v>70911</v>
       </c>
       <c r="F202">
-        <v>7618</v>
+        <v>8202</v>
       </c>
       <c r="G202">
         <v>53970</v>
@@ -7597,10 +7597,10 @@
         <v>149671</v>
       </c>
       <c r="I202">
-        <v>524393</v>
+        <v>523099</v>
       </c>
       <c r="J202">
-        <v>517774</v>
+        <v>517804</v>
       </c>
       <c r="K202" t="s">
         <v>53</v>
@@ -7614,16 +7614,16 @@
         <v>40</v>
       </c>
       <c r="C203">
-        <v>480</v>
+        <v>3720</v>
       </c>
       <c r="D203">
-        <v>58666</v>
+        <v>57524</v>
       </c>
       <c r="E203">
-        <v>58133</v>
+        <v>56528</v>
       </c>
       <c r="F203">
-        <v>8818</v>
+        <v>9768</v>
       </c>
       <c r="G203">
         <v>38807</v>
@@ -7632,10 +7632,10 @@
         <v>120317</v>
       </c>
       <c r="I203">
-        <v>451753</v>
+        <v>451711</v>
       </c>
       <c r="J203">
-        <v>445051</v>
+        <v>442686</v>
       </c>
       <c r="K203" t="s">
         <v>53</v>
@@ -7649,16 +7649,16 @@
         <v>40</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D204">
-        <v>39751</v>
+        <v>41573</v>
       </c>
       <c r="E204">
         <v>38481</v>
       </c>
       <c r="F204">
-        <v>3997</v>
+        <v>3395</v>
       </c>
       <c r="G204">
         <v>34760</v>
@@ -7667,10 +7667,10 @@
         <v>45045</v>
       </c>
       <c r="I204">
-        <v>245815</v>
+        <v>245680</v>
       </c>
       <c r="J204">
-        <v>243045</v>
+        <v>240975</v>
       </c>
       <c r="K204" t="s">
         <v>53</v>
@@ -7684,16 +7684,16 @@
         <v>40</v>
       </c>
       <c r="C205">
-        <v>204</v>
+        <v>1644</v>
       </c>
       <c r="D205">
-        <v>56624</v>
+        <v>55709</v>
       </c>
       <c r="E205">
-        <v>56500</v>
+        <v>55924</v>
       </c>
       <c r="F205">
-        <v>7818</v>
+        <v>6767</v>
       </c>
       <c r="G205">
         <v>9998</v>
@@ -7702,10 +7702,10 @@
         <v>94889</v>
       </c>
       <c r="I205">
-        <v>417036</v>
+        <v>415861</v>
       </c>
       <c r="J205">
-        <v>410356</v>
+        <v>410084</v>
       </c>
       <c r="K205" t="s">
         <v>53</v>
@@ -7719,16 +7719,16 @@
         <v>40</v>
       </c>
       <c r="C206">
-        <v>174</v>
+        <v>1038</v>
       </c>
       <c r="D206">
-        <v>48746</v>
+        <v>49087</v>
       </c>
       <c r="E206">
-        <v>49024</v>
+        <v>48546</v>
       </c>
       <c r="F206">
-        <v>6002</v>
+        <v>7511</v>
       </c>
       <c r="G206">
         <v>34285</v>
@@ -7737,10 +7737,10 @@
         <v>82722</v>
       </c>
       <c r="I206">
-        <v>379629</v>
+        <v>379691</v>
       </c>
       <c r="J206">
-        <v>372749</v>
+        <v>372298</v>
       </c>
       <c r="K206" t="s">
         <v>53</v>
@@ -7754,16 +7754,16 @@
         <v>40</v>
       </c>
       <c r="C207">
-        <v>78</v>
+        <v>678</v>
       </c>
       <c r="D207">
-        <v>49218</v>
+        <v>47674</v>
       </c>
       <c r="E207">
-        <v>48532</v>
+        <v>47117</v>
       </c>
       <c r="F207">
-        <v>6098</v>
+        <v>6060</v>
       </c>
       <c r="G207">
         <v>30958</v>
@@ -7772,10 +7772,10 @@
         <v>62121</v>
       </c>
       <c r="I207">
-        <v>346405</v>
+        <v>342950</v>
       </c>
       <c r="J207">
-        <v>339548</v>
+        <v>333349</v>
       </c>
       <c r="K207" t="s">
         <v>53</v>
@@ -7789,16 +7789,16 @@
         <v>40</v>
       </c>
       <c r="C208">
-        <v>17</v>
+        <v>161</v>
       </c>
       <c r="D208">
-        <v>43381</v>
+        <v>41582</v>
       </c>
       <c r="E208">
-        <v>42559</v>
+        <v>40302</v>
       </c>
       <c r="F208">
-        <v>6993</v>
+        <v>4122</v>
       </c>
       <c r="G208">
         <v>36593</v>
@@ -7807,10 +7807,10 @@
         <v>67163</v>
       </c>
       <c r="I208">
-        <v>271950</v>
+        <v>268173</v>
       </c>
       <c r="J208">
-        <v>266856</v>
+        <v>262022</v>
       </c>
       <c r="K208" t="s">
         <v>53</v>
@@ -7838,16 +7838,16 @@
         <v>40</v>
       </c>
       <c r="C210">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D210">
-        <v>78962</v>
+        <v>85126</v>
       </c>
       <c r="E210">
-        <v>78920</v>
+        <v>86287</v>
       </c>
       <c r="F210">
-        <v>5676</v>
+        <v>4598</v>
       </c>
       <c r="G210">
         <v>71124</v>
@@ -7856,10 +7856,10 @@
         <v>88073</v>
       </c>
       <c r="I210">
-        <v>544173</v>
+        <v>546957</v>
       </c>
       <c r="J210">
-        <v>544034</v>
+        <v>546184</v>
       </c>
       <c r="K210" t="s">
         <v>53</v>
